--- a/基本設計/09_システム管理_画面基本設計書.xlsx
+++ b/基本設計/09_システム管理_画面基本設計書.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rc898b02761204f76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rbedaa6480d2e405d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="Re651d6d9ee824b88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="Rcfda43010da44d65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="R0f19b70918a14c5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="R4a9f28662da44083"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-023_ユーザー管理" sheetId="19" r:id="R02288701270842d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-024_ロール管理" sheetId="20" r:id="Rb1c94f0ca61548f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-025_操作ログ" sheetId="21" r:id="Re0cb2fc4d1924dd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R9a031029883344d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R3227ee58bd8c4894"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R9165599ce83c4fae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="Rc51826dc10034008"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="Rf7ce88e50ee54f70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="R11e25f7d3cc24c4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-023_ユーザー管理" sheetId="19" r:id="Raef12ba676184aa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-024_ロール管理" sheetId="20" r:id="R89e74c01ee744269"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-025_操作ログ" sheetId="21" r:id="R0ae2358f96da49a7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1735,10 +1735,7 @@
       <x:c r="F16" s="319"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1754,25 +1751,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="362" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="362"/>
-      <x:c r="D19" s="362"/>
-      <x:c r="E19" s="362"/>
-      <x:c r="F19" s="362"/>
-      <x:c r="G19" s="362"/>
-      <x:c r="H19" s="362"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="362"/>
-      <x:c r="C20" s="362"/>
-      <x:c r="D20" s="362"/>
-      <x:c r="E20" s="362"/>
-      <x:c r="F20" s="362"/>
-      <x:c r="G20" s="362"/>
-      <x:c r="H20" s="362"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="362"/>
@@ -7010,54 +7004,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8694,54 +8656,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -10337,54 +10267,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/基本設計/09_システム管理_画面基本設計書.xlsx
+++ b/基本設計/09_システム管理_画面基本設計書.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R9a031029883344d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R3227ee58bd8c4894"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R9165599ce83c4fae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="Rc51826dc10034008"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="Rf7ce88e50ee54f70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="R11e25f7d3cc24c4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-023_ユーザー管理" sheetId="19" r:id="Raef12ba676184aa6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-024_ロール管理" sheetId="20" r:id="R89e74c01ee744269"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-025_操作ログ" sheetId="21" r:id="R0ae2358f96da49a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R753d40fa7eec4a51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R64710136e01547a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="R116e230552e14300"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="Rd2cbde0846294374"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-023_ユーザー管理" sheetId="19" r:id="R9d163de74612452a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-024_ロール管理" sheetId="20" r:id="Rfac28f3e7f5f4048"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-025_操作ログ" sheetId="21" r:id="Re5399bffebe34845"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_対象画面INDEX" sheetId="22" r:id="R9fd703cf90f84a95"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -24,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="35">
+  <x:fonts count="37">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -221,8 +220,19 @@
       <x:color rgb="FF1F1F1F"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF18283A"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FF193C61"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="35">
+  <x:fills count="37">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -394,8 +404,18 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234F77"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF1F5FA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="20">
+  <x:borders count="21">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -549,11 +569,25 @@
         <x:color rgb="FF8EA9C1"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="363">
+  <x:cellXfs count="380">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1305,6 +1339,53 @@
     <x:xf numFmtId="0" fontId="34" fillId="34" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="36" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1673,8 +1754,8 @@
     </x:row>
     <x:row r="11">
       <x:c r="B11"/>
-      <x:c r="C11" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C11" s="363" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1683,8 +1764,8 @@
       <x:c r="H11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="C12" s="357" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="C12" s="365" t="str">
+        <x:v>Document ID</x:v>
       </x:c>
       <x:c r="D12" s="319" t="str">
         <x:v>CW-BD-SCR-ADM</x:v>
@@ -1696,8 +1777,8 @@
       <x:c r="C13" s="357" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="D13" s="319" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="D13" s="366" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="E13" s="319"/>
       <x:c r="F13" s="319"/>
@@ -1706,8 +1787,8 @@
       <x:c r="C14" s="357" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="D14" s="319" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="D14" s="366" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="E14" s="319"/>
       <x:c r="F14" s="319"/>
@@ -1728,24 +1809,29 @@
       <x:c r="C16" s="357" t="str">
         <x:v>状態</x:v>
       </x:c>
-      <x:c r="D16" s="319" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="D16" s="366" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="E16" s="319"/>
       <x:c r="F16" s="319"/>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="368"/>
+      <x:c r="B17" s="368"/>
+      <x:c r="C17" s="368"/>
+      <x:c r="D17" s="368"/>
       <x:c r="E17"/>
       <x:c r="F17"/>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="368"/>
+      <x:c r="B18" s="368"/>
+      <x:c r="C18" s="368" t="str">
+        <x:v>Baseline ID</x:v>
+      </x:c>
+      <x:c r="D18" s="368" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
       <x:c r="E18"/>
       <x:c r="F18"/>
     </x:row>
@@ -1853,41 +1939,29 @@
       <x:c r="G2" s="300"/>
       <x:c r="H2" s="300"/>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="302" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="271" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="271"/>
-      <x:c r="D3" s="302" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="271" t="str">
-        <x:v>DOCUMENT-REVISION</x:v>
-      </x:c>
-      <x:c r="F3" s="271"/>
-      <x:c r="G3" s="271"/>
-      <x:c r="H3" s="271"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="302" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="271" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="271"/>
-      <x:c r="D4" s="302" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="271" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="271"/>
-      <x:c r="G4" s="271"/>
-      <x:c r="H4" s="271"/>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="369" t="str">
+        <x:v>システム名：Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="220"/>
+      <x:c r="C3" s="220"/>
+      <x:c r="D3" s="369"/>
+      <x:c r="E3" s="220"/>
+      <x:c r="F3" s="220"/>
+      <x:c r="G3" s="220"/>
+      <x:c r="H3" s="220"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="369" t="str">
+        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="220"/>
+      <x:c r="C4" s="220"/>
+      <x:c r="D4" s="369"/>
+      <x:c r="E4" s="220"/>
+      <x:c r="F4" s="220"/>
+      <x:c r="G4" s="220"/>
+      <x:c r="H4" s="220"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -1919,7 +1993,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="C7" s="309" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>改訂内容</x:v>
       </x:c>
       <x:c r="D7" s="309" t="str">
         <x:v>作成者</x:v>
@@ -1957,7 +2031,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G8" s="224" t="str">
-        <x:v>作成済</x:v>
+        <x:v>作成中</x:v>
       </x:c>
       <x:c r="H8" s="224" t="str">
         <x:v>基本設計初版</x:v>
@@ -1983,7 +2057,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G9" s="224" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H9" s="224" t="str">
         <x:v>Leader Review後Baseline化</x:v>
@@ -2009,7 +2083,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G10" s="224" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H10" s="224" t="str">
         <x:v>Review指摘対応</x:v>
@@ -2035,7 +2109,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G11" s="224" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H11" s="224" t="str">
         <x:v>再監査指摘対応</x:v>
@@ -2061,7 +2135,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G12" s="224" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H12" s="224" t="str">
         <x:v>再監査第2回指摘対応</x:v>
@@ -2086,8 +2160,8 @@
       <x:c r="F13" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G13" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G13" s="363" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H13" t="str">
         <x:v>再監査残項対応</x:v>
@@ -2112,8 +2186,8 @@
       <x:c r="F14" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G14" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G14" s="363" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>再Review指摘対応</x:v>
@@ -2138,747 +2212,107 @@
       <x:c r="F15" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G15" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G15" s="363" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H15" t="str">
         <x:v>最大10回の反復監査対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="110" customHeight="1">
+      <x:c r="A16" s="364" t="str">
+        <x:v>Ver.2.3</x:v>
+      </x:c>
+      <x:c r="B16" s="364" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C16" s="364" t="str">
+        <x:v>内容・関連Reviewの既確定仕様を整合。業務未決事項は承認待ちとして管理。</x:v>
+      </x:c>
+      <x:c r="D16" s="364" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E16" s="364" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F16" s="364" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G16" s="364" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H16" s="364" t="str">
+        <x:v>2026-09-18指摘対応。正式承認を示すものではない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="40" customHeight="1">
+      <x:c r="A17" s="364" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="B17" s="364" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C17" s="364" t="str">
+        <x:v>待確認12項目の方針選定、業務/API/DB/画面/運用を連動修正。章立て維持。</x:v>
+      </x:c>
+      <x:c r="D17" s="364" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E17" s="364" t="str">
+        <x:v>未実施</x:v>
+      </x:c>
+      <x:c r="F17" s="364" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G17" s="364" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H17" s="364" t="str">
+        <x:v>一般社内管理Systemの範囲。旧版はBackup保管。</x:v>
+      </x:c>
+      <x:c r="I17" s="364"/>
+      <x:c r="J17" s="364"/>
+      <x:c r="K17" s="364"/>
+      <x:c r="L17" s="364"/>
+    </x:row>
+    <x:row r="18" ht="100" customHeight="1">
+      <x:c r="A18" s="368" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B18" s="368" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="C18" s="368" t="str">
+        <x:v>共通規則・正本参照・構成・文書管理を統合修正。Baseline承認前の最終整合修正。</x:v>
+      </x:c>
+      <x:c r="D18" s="368" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E18" s="368" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F18" s="368" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G18" s="368" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H18" s="368" t="str">
+        <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
     <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A4:H4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="20" t="str">
-        <x:v>画面一覧</x:v>
-      </x:c>
-      <x:c r="B1" s="20"/>
-      <x:c r="C1" s="20"/>
-      <x:c r="D1" s="20"/>
-      <x:c r="E1" s="20"/>
-      <x:c r="F1" s="20"/>
-      <x:c r="G1" s="20"/>
-      <x:c r="H1" s="20"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="20"/>
-      <x:c r="B2" s="20"/>
-      <x:c r="C2" s="20"/>
-      <x:c r="D2" s="20"/>
-      <x:c r="E2" s="20"/>
-      <x:c r="F2" s="20"/>
-      <x:c r="G2" s="20"/>
-      <x:c r="H2" s="20"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="23" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="23"/>
-      <x:c r="C3" s="21" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="23"/>
-      <x:c r="G3" s="21" t="str">
-        <x:v>CW-BD-040</x:v>
-      </x:c>
-      <x:c r="H3" s="21"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="23" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="D4" s="21"/>
-      <x:c r="E4" s="23" t="str">
-        <x:v>作成日</x:v>
-      </x:c>
-      <x:c r="F4" s="23"/>
-      <x:c r="G4" s="24" t="n">
-        <x:v>46239</x:v>
-      </x:c>
-      <x:c r="H4" s="24"/>
-    </x:row>
-    <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="26" t="str">
-        <x:v>1. 画面一覧</x:v>
-      </x:c>
-      <x:c r="B6" s="26"/>
-      <x:c r="C6" s="26"/>
-      <x:c r="D6" s="26"/>
-      <x:c r="E6" s="26"/>
-      <x:c r="F6" s="26"/>
-      <x:c r="G6" s="26"/>
-      <x:c r="H6" s="26"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="31" t="str">
-        <x:v>画面ID</x:v>
-      </x:c>
-      <x:c r="B7" s="31" t="str">
-        <x:v>画面名</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="str">
-        <x:v>メニュー</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="str">
-        <x:v>利用ロール</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="str">
-        <x:v>種別</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="str">
-        <x:v>主要操作</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="str">
-        <x:v>関連機能</x:v>
-      </x:c>
-      <x:c r="H7" s="31" t="str">
-        <x:v>備考</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>SCR-023</x:v>
-      </x:c>
-      <x:c r="B8" s="33" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="str">
-        <x:v>システム管理</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E8" s="33" t="str">
-        <x:v>一覧/入力</x:v>
-      </x:c>
-      <x:c r="F8" s="33" t="str">
-        <x:v>M10</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="str">
-        <x:v>検索/詳細遷移</x:v>
-      </x:c>
-      <x:c r="H8" s="33"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>SCR-024</x:v>
-      </x:c>
-      <x:c r="B9" s="33" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="str">
-        <x:v>システム管理</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E9" s="33" t="str">
-        <x:v>一覧/入力</x:v>
-      </x:c>
-      <x:c r="F9" s="33" t="str">
-        <x:v>M10</x:v>
-      </x:c>
-      <x:c r="G9" s="33" t="str">
-        <x:v>検索/詳細遷移</x:v>
-      </x:c>
-      <x:c r="H9" s="33"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>SCR-025</x:v>
-      </x:c>
-      <x:c r="B10" s="33" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="str">
-        <x:v>システム管理</x:v>
-      </x:c>
-      <x:c r="D10" s="33" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E10" s="33" t="str">
-        <x:v>一覧</x:v>
-      </x:c>
-      <x:c r="F10" s="33" t="str">
-        <x:v>M11</x:v>
-      </x:c>
-      <x:c r="G10" s="33" t="str">
-        <x:v>検索/詳細遷移</x:v>
-      </x:c>
-      <x:c r="H10" s="33"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11"/>
-      <x:c r="B11"/>
-      <x:c r="C11"/>
-      <x:c r="D11"/>
-      <x:c r="E11"/>
-      <x:c r="F11"/>
-      <x:c r="G11"/>
-      <x:c r="H11"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12"/>
-      <x:c r="B12"/>
-      <x:c r="C12"/>
-      <x:c r="D12"/>
-      <x:c r="E12"/>
-      <x:c r="F12"/>
-      <x:c r="G12"/>
-      <x:c r="H12"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13"/>
-      <x:c r="B13"/>
-      <x:c r="C13"/>
-      <x:c r="D13"/>
-      <x:c r="E13"/>
-      <x:c r="F13"/>
-      <x:c r="G13"/>
-      <x:c r="H13"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14"/>
-      <x:c r="B14"/>
-      <x:c r="C14"/>
-      <x:c r="D14"/>
-      <x:c r="E14"/>
-      <x:c r="F14"/>
-      <x:c r="G14"/>
-      <x:c r="H14"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15"/>
-      <x:c r="B15"/>
-      <x:c r="C15"/>
-      <x:c r="D15"/>
-      <x:c r="E15"/>
-      <x:c r="F15"/>
-      <x:c r="G15"/>
-      <x:c r="H15"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16"/>
-      <x:c r="B16"/>
-      <x:c r="C16"/>
-      <x:c r="D16"/>
-      <x:c r="E16"/>
-      <x:c r="F16"/>
-      <x:c r="G16"/>
-      <x:c r="H16"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="B17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
-      <x:c r="E17"/>
-      <x:c r="F17"/>
-      <x:c r="G17"/>
-      <x:c r="H17"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
-      <x:c r="E18"/>
-      <x:c r="F18"/>
-      <x:c r="G18"/>
-      <x:c r="H18"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19"/>
-      <x:c r="B19"/>
-      <x:c r="C19"/>
-      <x:c r="D19"/>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20"/>
-      <x:c r="B20"/>
-      <x:c r="C20"/>
-      <x:c r="D20"/>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
-      <x:c r="G20"/>
-      <x:c r="H20"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21"/>
-      <x:c r="B21"/>
-      <x:c r="C21"/>
-      <x:c r="D21"/>
-      <x:c r="E21"/>
-      <x:c r="F21"/>
-      <x:c r="G21"/>
-      <x:c r="H21"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22"/>
-      <x:c r="B22"/>
-      <x:c r="C22"/>
-      <x:c r="D22"/>
-      <x:c r="E22"/>
-      <x:c r="F22"/>
-      <x:c r="G22"/>
-      <x:c r="H22"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23"/>
-      <x:c r="B23"/>
-      <x:c r="C23"/>
-      <x:c r="D23"/>
-      <x:c r="E23"/>
-      <x:c r="F23"/>
-      <x:c r="G23"/>
-      <x:c r="H23"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24"/>
-      <x:c r="B24"/>
-      <x:c r="C24"/>
-      <x:c r="D24"/>
-      <x:c r="E24"/>
-      <x:c r="F24"/>
-      <x:c r="G24"/>
-      <x:c r="H24"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25"/>
-      <x:c r="B25"/>
-      <x:c r="C25"/>
-      <x:c r="D25"/>
-      <x:c r="E25"/>
-      <x:c r="F25"/>
-      <x:c r="G25"/>
-      <x:c r="H25"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26"/>
-      <x:c r="B26"/>
-      <x:c r="C26"/>
-      <x:c r="D26"/>
-      <x:c r="E26"/>
-      <x:c r="F26"/>
-      <x:c r="G26"/>
-      <x:c r="H26"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27"/>
-      <x:c r="B27"/>
-      <x:c r="C27"/>
-      <x:c r="D27"/>
-      <x:c r="E27"/>
-      <x:c r="F27"/>
-      <x:c r="G27"/>
-      <x:c r="H27"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28"/>
-      <x:c r="B28"/>
-      <x:c r="C28"/>
-      <x:c r="D28"/>
-      <x:c r="E28"/>
-      <x:c r="F28"/>
-      <x:c r="G28"/>
-      <x:c r="H28"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29"/>
-      <x:c r="B29"/>
-      <x:c r="C29"/>
-      <x:c r="D29"/>
-      <x:c r="E29"/>
-      <x:c r="F29"/>
-      <x:c r="G29"/>
-      <x:c r="H29"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30"/>
-      <x:c r="B30"/>
-      <x:c r="C30"/>
-      <x:c r="D30"/>
-      <x:c r="E30"/>
-      <x:c r="F30"/>
-      <x:c r="G30"/>
-      <x:c r="H30"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31"/>
-      <x:c r="B31"/>
-      <x:c r="C31"/>
-      <x:c r="D31"/>
-      <x:c r="E31"/>
-      <x:c r="F31"/>
-      <x:c r="G31"/>
-      <x:c r="H31"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32"/>
-      <x:c r="B32"/>
-      <x:c r="C32"/>
-      <x:c r="D32"/>
-      <x:c r="E32"/>
-      <x:c r="F32"/>
-      <x:c r="G32"/>
-      <x:c r="H32"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33"/>
-      <x:c r="B33"/>
-      <x:c r="C33"/>
-      <x:c r="D33"/>
-      <x:c r="E33"/>
-      <x:c r="F33"/>
-      <x:c r="G33"/>
-      <x:c r="H33"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
-    <x:mergeCell ref="A6:H6"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="7" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="40" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="20" t="str">
-        <x:v>画面遷移</x:v>
-      </x:c>
-      <x:c r="B1" s="20"/>
-      <x:c r="C1" s="20"/>
-      <x:c r="D1" s="20"/>
-      <x:c r="E1" s="20"/>
-      <x:c r="F1" s="20"/>
-      <x:c r="G1" s="20"/>
-      <x:c r="H1" s="20"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="20"/>
-      <x:c r="B2" s="20"/>
-      <x:c r="C2" s="20"/>
-      <x:c r="D2" s="20"/>
-      <x:c r="E2" s="20"/>
-      <x:c r="F2" s="20"/>
-      <x:c r="G2" s="20"/>
-      <x:c r="H2" s="20"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="23" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="23"/>
-      <x:c r="C3" s="21" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="23"/>
-      <x:c r="G3" s="21" t="str">
-        <x:v>CW-BD-041</x:v>
-      </x:c>
-      <x:c r="H3" s="21"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="23" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="D4" s="21"/>
-      <x:c r="E4" s="23" t="str">
-        <x:v>作成日</x:v>
-      </x:c>
-      <x:c r="F4" s="23"/>
-      <x:c r="G4" s="24" t="n">
-        <x:v>46239</x:v>
-      </x:c>
-      <x:c r="H4" s="24"/>
-    </x:row>
-    <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="26" t="str">
-        <x:v>1. 主要画面遷移</x:v>
-      </x:c>
-      <x:c r="B6" s="26"/>
-      <x:c r="C6" s="26"/>
-      <x:c r="D6" s="26"/>
-      <x:c r="E6" s="26"/>
-      <x:c r="F6" s="26"/>
-      <x:c r="G6" s="26"/>
-      <x:c r="H6" s="26"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="31" t="str">
-        <x:v>No.</x:v>
-      </x:c>
-      <x:c r="B7" s="31" t="str">
-        <x:v>遷移元</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="str">
-        <x:v>イベント</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="str">
-        <x:v>遷移先</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="str">
-        <x:v>引継情報</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="str">
-        <x:v>権限・条件</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="str">
-        <x:v>戻る動作</x:v>
-      </x:c>
-      <x:c r="H7" s="31" t="str">
-        <x:v>備考</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8"/>
-      <x:c r="B8"/>
-      <x:c r="C8"/>
-      <x:c r="D8"/>
-      <x:c r="E8"/>
-      <x:c r="F8"/>
-      <x:c r="G8"/>
-      <x:c r="H8"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9"/>
-      <x:c r="B9"/>
-      <x:c r="C9"/>
-      <x:c r="D9"/>
-      <x:c r="E9"/>
-      <x:c r="F9"/>
-      <x:c r="G9"/>
-      <x:c r="H9"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10"/>
-      <x:c r="B10"/>
-      <x:c r="C10"/>
-      <x:c r="D10"/>
-      <x:c r="E10"/>
-      <x:c r="F10"/>
-      <x:c r="G10"/>
-      <x:c r="H10"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11"/>
-      <x:c r="B11"/>
-      <x:c r="C11"/>
-      <x:c r="D11"/>
-      <x:c r="E11"/>
-      <x:c r="F11"/>
-      <x:c r="G11"/>
-      <x:c r="H11"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12"/>
-      <x:c r="B12"/>
-      <x:c r="C12"/>
-      <x:c r="D12"/>
-      <x:c r="E12"/>
-      <x:c r="F12"/>
-      <x:c r="G12"/>
-      <x:c r="H12"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13"/>
-      <x:c r="B13"/>
-      <x:c r="C13"/>
-      <x:c r="D13"/>
-      <x:c r="E13"/>
-      <x:c r="F13"/>
-      <x:c r="G13"/>
-      <x:c r="H13"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14"/>
-      <x:c r="B14"/>
-      <x:c r="C14"/>
-      <x:c r="D14"/>
-      <x:c r="E14"/>
-      <x:c r="F14"/>
-      <x:c r="G14"/>
-      <x:c r="H14"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15"/>
-      <x:c r="B15"/>
-      <x:c r="C15"/>
-      <x:c r="D15"/>
-      <x:c r="E15"/>
-      <x:c r="F15"/>
-      <x:c r="G15"/>
-      <x:c r="H15"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16"/>
-      <x:c r="B16"/>
-      <x:c r="C16"/>
-      <x:c r="D16"/>
-      <x:c r="E16"/>
-      <x:c r="F16"/>
-      <x:c r="G16"/>
-      <x:c r="H16"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="B17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
-      <x:c r="E17"/>
-      <x:c r="F17"/>
-      <x:c r="G17"/>
-      <x:c r="H17"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
-      <x:c r="E18"/>
-      <x:c r="F18"/>
-      <x:c r="G18"/>
-      <x:c r="H18"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19"/>
-      <x:c r="B19"/>
-      <x:c r="C19"/>
-      <x:c r="D19"/>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20"/>
-      <x:c r="B20"/>
-      <x:c r="C20"/>
-      <x:c r="D20"/>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
-      <x:c r="G20"/>
-      <x:c r="H20"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21"/>
-      <x:c r="B21"/>
-      <x:c r="C21"/>
-      <x:c r="D21"/>
-      <x:c r="E21"/>
-      <x:c r="F21"/>
-      <x:c r="G21"/>
-      <x:c r="H21"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22"/>
-      <x:c r="B22"/>
-      <x:c r="C22"/>
-      <x:c r="D22"/>
-      <x:c r="E22"/>
-      <x:c r="F22"/>
-      <x:c r="G22"/>
-      <x:c r="H22"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23"/>
-      <x:c r="B23"/>
-      <x:c r="C23"/>
-      <x:c r="D23"/>
-      <x:c r="E23"/>
-      <x:c r="F23"/>
-      <x:c r="G23"/>
-      <x:c r="H23"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
-    <x:mergeCell ref="A6:H6"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -2930,15 +2364,11 @@
       <x:c r="A3" s="219" t="str">
         <x:v>システム名</x:v>
       </x:c>
-      <x:c r="B3" s="220" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
+      <x:c r="B3" s="220" t="str"/>
       <x:c r="C3" s="220"/>
       <x:c r="D3" s="220"/>
       <x:c r="E3" s="220"/>
-      <x:c r="F3" s="219" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
+      <x:c r="F3" s="219" t="str"/>
       <x:c r="G3" s="220" t="str">
         <x:v>CW-BD-043</x:v>
       </x:c>
@@ -2949,20 +2379,16 @@
       <x:c r="L3" s="220"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="219" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="220" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
+      <x:c r="A4" s="369" t="str">
+        <x:v>版数：Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B4" s="220"/>
       <x:c r="C4" s="220"/>
       <x:c r="D4" s="220"/>
       <x:c r="E4" s="220"/>
-      <x:c r="F4" s="219" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
+      <x:c r="F4" s="219" t="str"/>
       <x:c r="G4" s="220" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="H4" s="220"/>
       <x:c r="I4" s="220"/>
@@ -3034,9 +2460,7 @@
       <x:c r="K7" s="223" t="str">
         <x:v>関連API.Field</x:v>
       </x:c>
-      <x:c r="L7" s="223" t="str">
-        <x:v>DB/Response</x:v>
-      </x:c>
+      <x:c r="L7" s="223"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="224" t="str">
@@ -3070,11 +2494,9 @@
         <x:v>部分一致</x:v>
       </x:c>
       <x:c r="K8" s="224" t="str">
-        <x:v>API-USR-001.username</x:v>
-      </x:c>
-      <x:c r="L8" s="224" t="str">
-        <x:v>users.username</x:v>
-      </x:c>
+        <x:v>API-USR-001.request.query.username</x:v>
+      </x:c>
+      <x:c r="L8" s="224"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="224" t="str">
@@ -3108,11 +2530,9 @@
         <x:v>部分一致</x:v>
       </x:c>
       <x:c r="K9" s="224" t="str">
-        <x:v>API-USR-001.name</x:v>
-      </x:c>
-      <x:c r="L9" s="224" t="str">
-        <x:v>employees.name</x:v>
-      </x:c>
+        <x:v>API-USR-001.request.query.name</x:v>
+      </x:c>
+      <x:c r="L9" s="224"/>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="224" t="str">
@@ -3146,11 +2566,9 @@
         <x:v>有効/無効</x:v>
       </x:c>
       <x:c r="K10" s="224" t="str">
-        <x:v>API-USR-001.status</x:v>
-      </x:c>
-      <x:c r="L10" s="224" t="str">
-        <x:v>users.enabled</x:v>
-      </x:c>
+        <x:v>API-USR-001.request.query.status</x:v>
+      </x:c>
+      <x:c r="L10" s="224"/>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="224" t="str">
@@ -3184,11 +2602,9 @@
         <x:v>lockedUntil判定</x:v>
       </x:c>
       <x:c r="K11" s="224" t="str">
-        <x:v>API-USR-001.locked</x:v>
-      </x:c>
-      <x:c r="L11" s="224" t="str">
-        <x:v>users.locked_until</x:v>
-      </x:c>
+        <x:v>API-USR-001.request.query.locked</x:v>
+      </x:c>
+      <x:c r="L11" s="224"/>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="224" t="str">
@@ -3224,9 +2640,7 @@
       <x:c r="K12" s="224" t="str">
         <x:v>API-USR-001</x:v>
       </x:c>
-      <x:c r="L12" s="224" t="str">
-        <x:v>users</x:v>
-      </x:c>
+      <x:c r="L12" s="224"/>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="224" t="str">
@@ -3260,11 +2674,9 @@
         <x:v>自身停止禁止</x:v>
       </x:c>
       <x:c r="K13" s="224" t="str">
-        <x:v>API-USR-003.enabled</x:v>
-      </x:c>
-      <x:c r="L13" s="224" t="str">
-        <x:v>users.enabled</x:v>
-      </x:c>
+        <x:v>API-USR-003.request.body.enabled</x:v>
+      </x:c>
+      <x:c r="L13" s="224"/>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="224" t="str">
@@ -3298,11 +2710,9 @@
         <x:v>自身ADMIN剥奪禁止</x:v>
       </x:c>
       <x:c r="K14" s="224" t="str">
-        <x:v>API-USR-003.roleIds</x:v>
-      </x:c>
-      <x:c r="L14" s="224" t="str">
-        <x:v>user_roles</x:v>
-      </x:c>
+        <x:v>API-USR-003.request.body.roleIds</x:v>
+      </x:c>
+      <x:c r="L14" s="224"/>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="224" t="str">
@@ -3336,11 +2746,9 @@
         <x:v>VAL-010</x:v>
       </x:c>
       <x:c r="K15" s="224" t="str">
-        <x:v>API-USR-003.version</x:v>
-      </x:c>
-      <x:c r="L15" s="224" t="str">
-        <x:v>users.version</x:v>
-      </x:c>
+        <x:v>API-USR-003.request.body.version</x:v>
+      </x:c>
+      <x:c r="L15" s="224"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
       <x:c r="A16" s="224" t="str">
@@ -3376,9 +2784,7 @@
       <x:c r="K16" s="224" t="str">
         <x:v>API-USR-004</x:v>
       </x:c>
-      <x:c r="L16" s="224" t="str">
-        <x:v>users</x:v>
-      </x:c>
+      <x:c r="L16" s="224"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
       <x:c r="A17" s="224" t="str">
@@ -3412,11 +2818,9 @@
         <x:v>一意/更新不可</x:v>
       </x:c>
       <x:c r="K17" s="224" t="str">
-        <x:v>API-ROLE-003.roleCode</x:v>
-      </x:c>
-      <x:c r="L17" s="224" t="str">
-        <x:v>roles.role_code</x:v>
-      </x:c>
+        <x:v>API-ROLE-003.request.body.roleCode</x:v>
+      </x:c>
+      <x:c r="L17" s="224"/>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
       <x:c r="A18" s="224" t="str">
@@ -3452,9 +2856,7 @@
       <x:c r="K18" s="224" t="str">
         <x:v>API-ROLE-003, API-ROLE-004.roleName</x:v>
       </x:c>
-      <x:c r="L18" s="224" t="str">
-        <x:v>roles.role_name</x:v>
-      </x:c>
+      <x:c r="L18" s="224"/>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
       <x:c r="A19" s="224" t="str">
@@ -3490,9 +2892,7 @@
       <x:c r="K19" s="224" t="str">
         <x:v>API-ROLE-003, API-ROLE-004.description</x:v>
       </x:c>
-      <x:c r="L19" s="224" t="str">
-        <x:v>roles.description</x:v>
-      </x:c>
+      <x:c r="L19" s="224"/>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
       <x:c r="A20" s="224" t="str">
@@ -3526,11 +2926,9 @@
         <x:v>状態定義</x:v>
       </x:c>
       <x:c r="K20" s="224" t="str">
-        <x:v>API-ROLE-005.status</x:v>
-      </x:c>
-      <x:c r="L20" s="224" t="str">
-        <x:v>roles.status</x:v>
-      </x:c>
+        <x:v>API-ROLE-005.request.body.status</x:v>
+      </x:c>
+      <x:c r="L20" s="224"/>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
       <x:c r="A21" s="224" t="str">
@@ -3566,9 +2964,7 @@
       <x:c r="K21" s="224" t="str">
         <x:v>API-ROLE-003, API-ROLE-004.permissionIds</x:v>
       </x:c>
-      <x:c r="L21" s="224" t="str">
-        <x:v>role_permissions</x:v>
-      </x:c>
+      <x:c r="L21" s="224"/>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
       <x:c r="A22" s="224" t="str">
@@ -3604,9 +3000,7 @@
       <x:c r="K22" s="224" t="str">
         <x:v>API-ROLE-004, API-ROLE-005.version</x:v>
       </x:c>
-      <x:c r="L22" s="224" t="str">
-        <x:v>roles.version</x:v>
-      </x:c>
+      <x:c r="L22" s="224"/>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
       <x:c r="A23" s="224" t="str">
@@ -3640,11 +3034,9 @@
         <x:v>期間31日以内</x:v>
       </x:c>
       <x:c r="K23" s="224" t="str">
-        <x:v>API-LOG-001.from</x:v>
-      </x:c>
-      <x:c r="L23" s="224" t="str">
-        <x:v>operation_logs.created_at</x:v>
-      </x:c>
+        <x:v>API-LOG-001.request.query.from</x:v>
+      </x:c>
+      <x:c r="L23" s="224"/>
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
       <x:c r="A24" s="224" t="str">
@@ -3678,11 +3070,9 @@
         <x:v>期間31日以内</x:v>
       </x:c>
       <x:c r="K24" s="224" t="str">
-        <x:v>API-LOG-001.to</x:v>
-      </x:c>
-      <x:c r="L24" s="224" t="str">
-        <x:v>operation_logs.created_at</x:v>
-      </x:c>
+        <x:v>API-LOG-001.request.query.to</x:v>
+      </x:c>
+      <x:c r="L24" s="224"/>
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
       <x:c r="A25" s="224" t="str">
@@ -3716,11 +3106,9 @@
         <x:v>管理者のみ</x:v>
       </x:c>
       <x:c r="K25" s="224" t="str">
-        <x:v>API-LOG-001.userId</x:v>
-      </x:c>
-      <x:c r="L25" s="224" t="str">
-        <x:v>operation_logs.user_id</x:v>
-      </x:c>
+        <x:v>API-LOG-001.request.query.userId</x:v>
+      </x:c>
+      <x:c r="L25" s="224"/>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
       <x:c r="A26" s="224" t="str">
@@ -3754,11 +3142,9 @@
         <x:v>Module定義</x:v>
       </x:c>
       <x:c r="K26" s="224" t="str">
-        <x:v>API-LOG-001.module</x:v>
-      </x:c>
-      <x:c r="L26" s="224" t="str">
-        <x:v>operation_logs.module</x:v>
-      </x:c>
+        <x:v>API-LOG-001.request.query.module</x:v>
+      </x:c>
+      <x:c r="L26" s="224"/>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
       <x:c r="A27" s="224" t="str">
@@ -3792,11 +3178,9 @@
         <x:v>Action定義</x:v>
       </x:c>
       <x:c r="K27" s="224" t="str">
-        <x:v>API-LOG-001.action</x:v>
-      </x:c>
-      <x:c r="L27" s="224" t="str">
-        <x:v>operation_logs.action</x:v>
-      </x:c>
+        <x:v>API-LOG-001.request.query.action</x:v>
+      </x:c>
+      <x:c r="L27" s="224"/>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
       <x:c r="A28" s="224" t="str">
@@ -3821,7 +3205,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="H28" s="224" t="str">
-        <x:v>SUCCESS/FAIL</x:v>
+        <x:v>SUCCESS/FAILURE</x:v>
       </x:c>
       <x:c r="I28" s="224" t="str">
         <x:v>全て</x:v>
@@ -3830,11 +3214,9 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="K28" s="224" t="str">
-        <x:v>API-LOG-001.result</x:v>
-      </x:c>
-      <x:c r="L28" s="224" t="str">
-        <x:v>operation_logs.operation_result</x:v>
-      </x:c>
+        <x:v>API-LOG-001.request.query.result</x:v>
+      </x:c>
+      <x:c r="L28" s="224"/>
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
       <x:c r="A29" s="224" t="str">
@@ -3868,11 +3250,9 @@
         <x:v>完全一致</x:v>
       </x:c>
       <x:c r="K29" s="224" t="str">
-        <x:v>API-LOG-001.traceId</x:v>
-      </x:c>
-      <x:c r="L29" s="224" t="str">
-        <x:v>operation_logs.trace_id</x:v>
-      </x:c>
+        <x:v>API-LOG-001.request.query.traceId</x:v>
+      </x:c>
+      <x:c r="L29" s="224"/>
     </x:row>
     <x:row r="30" ht="30" customHeight="1">
       <x:c r="A30" s="224" t="str">
@@ -3908,21 +3288,43 @@
       <x:c r="K30" s="224" t="str">
         <x:v>API-LOG-001</x:v>
       </x:c>
-      <x:c r="L30" s="224" t="str">
-        <x:v>operation_logs</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31"/>
-      <x:c r="B31"/>
-      <x:c r="C31"/>
-      <x:c r="D31"/>
-      <x:c r="E31"/>
-      <x:c r="F31"/>
-      <x:c r="G31"/>
-      <x:c r="H31"/>
-      <x:c r="I31"/>
-      <x:c r="J31"/>
+      <x:c r="L30" s="224"/>
+    </x:row>
+    <x:row r="31" ht="110" customHeight="1">
+      <x:c r="A31" s="364" t="str">
+        <x:v>SCR-025</x:v>
+      </x:c>
+      <x:c r="B31" s="364" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C31" s="364" t="str">
+        <x:v>auditChanges</x:v>
+      </x:c>
+      <x:c r="D31" s="364" t="str">
+        <x:v>変更前後値</x:v>
+      </x:c>
+      <x:c r="E31" s="364" t="str">
+        <x:v>Detail</x:v>
+      </x:c>
+      <x:c r="F31" s="364" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="G31" s="364" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H31" s="364" t="str">
+        <x:v>JSON業務項目</x:v>
+      </x:c>
+      <x:c r="I31" s="364" t="str">
+        <x:v>取得値</x:v>
+      </x:c>
+      <x:c r="J31" s="364" t="str">
+        <x:v>管理者のみ。Nullは「記録対象外」。Password/Token等は表示しない</x:v>
+      </x:c>
+      <x:c r="K31" s="364" t="str">
+        <x:v>API-LOG-002.beforeValues/afterValues</x:v>
+      </x:c>
+      <x:c r="L31" s="364"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32"/>
@@ -4915,7 +4317,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4955,13 +4357,9 @@
       <x:c r="A3" s="219" t="str">
         <x:v>システム名</x:v>
       </x:c>
-      <x:c r="B3" s="220" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
+      <x:c r="B3" s="220" t="str"/>
       <x:c r="C3" s="220"/>
-      <x:c r="D3" s="219" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
+      <x:c r="D3" s="219" t="str"/>
       <x:c r="E3" s="220" t="str">
         <x:v>CW-BD-045</x:v>
       </x:c>
@@ -4970,18 +4368,14 @@
       <x:c r="H3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="219" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="220" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
+      <x:c r="A4" s="369" t="str">
+        <x:v>版数：Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B4" s="220"/>
       <x:c r="C4" s="220"/>
-      <x:c r="D4" s="219" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
+      <x:c r="D4" s="219" t="str"/>
       <x:c r="E4" s="220" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="220"/>
       <x:c r="G4" s="220"/>
@@ -5080,7 +4474,7 @@
       </x:c>
       <x:c r="H9"/>
     </x:row>
-    <x:row r="10" ht="30" customHeight="1">
+    <x:row r="10" ht="96" customHeight="1">
       <x:c r="A10" s="224" t="str">
         <x:v>SCR-023</x:v>
       </x:c>
@@ -5094,7 +4488,8 @@
         <x:v>API-USR-003</x:v>
       </x:c>
       <x:c r="E10" s="224" t="str">
-        <x:v>自身ADMIN保護→version付き更新→再検索</x:v>
+        <x:v>自身ADMIN保護→version付き更新→再検索
+全Userに内蔵Roleを1つ以上。停止Role割当禁止。自身停止/ADMIN剥奪と最後の有効ADMIN喪失を禁止。担当中PJのPMからROLE-PMを外す・User停止する場合は先にPM交替。</x:v>
       </x:c>
       <x:c r="F10" s="224" t="str">
         <x:v>400/409</x:v>
@@ -5102,9 +4497,13 @@
       <x:c r="G10" s="224" t="str">
         <x:v>Button非活性</x:v>
       </x:c>
-      <x:c r="H10"/>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
+      <x:c r="H10" s="364"/>
+      <x:c r="I10" s="364"/>
+      <x:c r="J10" s="364"/>
+      <x:c r="K10" s="364"/>
+      <x:c r="L10" s="364"/>
+    </x:row>
+    <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="224" t="str">
         <x:v>SCR-023</x:v>
       </x:c>
@@ -5118,7 +4517,8 @@
         <x:v>API-USR-004</x:v>
       </x:c>
       <x:c r="E11" s="224" t="str">
-        <x:v>確認→一時Password一回表示</x:v>
+        <x:v>確認→一時Password一回表示
+同Key再送はReset再実行なし、temporaryPassword=null。18／32の固定案内。</x:v>
       </x:c>
       <x:c r="F11" s="224" t="str">
         <x:v>404/409</x:v>
@@ -5126,7 +4526,11 @@
       <x:c r="G11" s="224" t="str">
         <x:v>Idempotency Key</x:v>
       </x:c>
-      <x:c r="H11"/>
+      <x:c r="H11" s="364"/>
+      <x:c r="I11" s="364"/>
+      <x:c r="J11" s="364"/>
+      <x:c r="K11" s="364"/>
+      <x:c r="L11" s="364"/>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="224" t="str">
@@ -5152,7 +4556,7 @@
       </x:c>
       <x:c r="H12"/>
     </x:row>
-    <x:row r="13" ht="30" customHeight="1">
+    <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="224" t="str">
         <x:v>SCR-024</x:v>
       </x:c>
@@ -5166,7 +4570,7 @@
         <x:v>API-ROLE-003</x:v>
       </x:c>
       <x:c r="E13" s="224" t="str">
-        <x:v>検証→Role/Permission登録</x:v>
+        <x:v>カスタムRoleのみACTIVEで登録。組込Code再使用不可。Permissionは既存17Codeから選択。</x:v>
       </x:c>
       <x:c r="F13" s="224" t="str">
         <x:v>重複Error</x:v>
@@ -5174,9 +4578,13 @@
       <x:c r="G13" s="224" t="str">
         <x:v>Idempotency Key</x:v>
       </x:c>
-      <x:c r="H13"/>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
+      <x:c r="H13" s="364"/>
+      <x:c r="I13" s="364"/>
+      <x:c r="J13" s="364"/>
+      <x:c r="K13" s="364"/>
+      <x:c r="L13" s="364"/>
+    </x:row>
+    <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="224" t="str">
         <x:v>SCR-024</x:v>
       </x:c>
@@ -5190,7 +4598,7 @@
         <x:v>API-ROLE-004</x:v>
       </x:c>
       <x:c r="E14" s="224" t="str">
-        <x:v>組込Code保護→version付き更新→Cache削除</x:v>
+        <x:v>Codeは全Role変更不可。組込Roleは名称/説明だけ編集可、Permissionは表示専用。version付き更新後、権限Cacheを失効。</x:v>
       </x:c>
       <x:c r="F14" s="224" t="str">
         <x:v>409</x:v>
@@ -5198,9 +4606,13 @@
       <x:c r="G14" s="224" t="str">
         <x:v>Button非活性</x:v>
       </x:c>
-      <x:c r="H14"/>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
+      <x:c r="H14" s="364"/>
+      <x:c r="I14" s="364"/>
+      <x:c r="J14" s="364"/>
+      <x:c r="K14" s="364"/>
+      <x:c r="L14" s="364"/>
+    </x:row>
+    <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="224" t="str">
         <x:v>SCR-024</x:v>
       </x:c>
@@ -5214,7 +4626,7 @@
         <x:v>API-ROLE-005</x:v>
       </x:c>
       <x:c r="E15" s="224" t="str">
-        <x:v>使用状況確認→状態変更</x:v>
+        <x:v>組込Roleの状態Buttonは非活性。カスタムRole停止はUser割当0件のみ。停止後再開可。同状態指定は変更せずCOMMON-4000。失敗時旧値保持。</x:v>
       </x:c>
       <x:c r="F15" s="224" t="str">
         <x:v>409</x:v>
@@ -5222,7 +4634,11 @@
       <x:c r="G15" s="224" t="str">
         <x:v>Button非活性</x:v>
       </x:c>
-      <x:c r="H15"/>
+      <x:c r="H15" s="364"/>
+      <x:c r="I15" s="364"/>
+      <x:c r="J15" s="364"/>
+      <x:c r="K15" s="364"/>
+      <x:c r="L15" s="364"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
       <x:c r="A16" s="224" t="str">
@@ -5451,7 +4867,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -5477,101 +4893,43 @@
       <x:c r="A1" s="52" t="str">
         <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
       </x:c>
-      <x:c r="B1" s="52" t="str">
-        <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="C1" s="52" t="str">
-        <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="D1" s="52" t="str">
-        <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="E1" s="52" t="str">
-        <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="F1" s="52" t="str">
-        <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="G1" s="52" t="str">
-        <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="H1" s="52" t="str">
-        <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="I1" s="52" t="str">
-        <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="J1" s="52" t="str">
-        <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="K1" s="52" t="str">
-        <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="L1" s="52" t="str">
-        <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="M1" s="52" t="str">
-        <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="N1" s="52" t="str">
-        <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="O1" s="52" t="str">
-        <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="P1" s="52" t="str">
-        <x:v>SCR-023  ユーザー管理  画面レイアウト</x:v>
-      </x:c>
+      <x:c r="B1" s="52" t="str"/>
+      <x:c r="C1" s="52" t="str"/>
+      <x:c r="D1" s="52" t="str"/>
+      <x:c r="E1" s="52" t="str"/>
+      <x:c r="F1" s="52" t="str"/>
+      <x:c r="G1" s="52" t="str"/>
+      <x:c r="H1" s="52" t="str"/>
+      <x:c r="I1" s="52" t="str"/>
+      <x:c r="J1" s="52" t="str"/>
+      <x:c r="K1" s="52" t="str"/>
+      <x:c r="L1" s="52" t="str"/>
+      <x:c r="M1" s="52" t="str"/>
+      <x:c r="N1" s="52" t="str"/>
+      <x:c r="O1" s="52" t="str"/>
+      <x:c r="P1" s="52" t="str"/>
     </x:row>
     <x:row r="2" ht="21" customHeight="1">
       <x:c r="A2" s="54" t="str">
         <x:v>画面ID: SCR-023    画面名: ユーザー管理</x:v>
       </x:c>
-      <x:c r="B2" s="54" t="str">
-        <x:v>画面ID: SCR-023    画面名: ユーザー管理</x:v>
-      </x:c>
-      <x:c r="C2" s="54" t="str">
-        <x:v>画面ID: SCR-023    画面名: ユーザー管理</x:v>
-      </x:c>
-      <x:c r="D2" s="54" t="str">
-        <x:v>画面ID: SCR-023    画面名: ユーザー管理</x:v>
-      </x:c>
-      <x:c r="E2" s="54" t="str">
-        <x:v>画面ID: SCR-023    画面名: ユーザー管理</x:v>
-      </x:c>
-      <x:c r="F2" s="54" t="str">
-        <x:v>画面ID: SCR-023    画面名: ユーザー管理</x:v>
-      </x:c>
-      <x:c r="G2" s="54" t="str">
-        <x:v>画面ID: SCR-023    画面名: ユーザー管理</x:v>
-      </x:c>
-      <x:c r="H2" s="54" t="str">
-        <x:v>画面ID: SCR-023    画面名: ユーザー管理</x:v>
-      </x:c>
-      <x:c r="I2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="J2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="K2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="L2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="M2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="N2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="O2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="P2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
+      <x:c r="B2" s="54" t="str"/>
+      <x:c r="C2" s="54" t="str"/>
+      <x:c r="D2" s="54" t="str"/>
+      <x:c r="E2" s="54" t="str"/>
+      <x:c r="F2" s="54" t="str"/>
+      <x:c r="G2" s="54" t="str"/>
+      <x:c r="H2" s="54" t="str"/>
+      <x:c r="I2" s="370" t="str">
+        <x:v>Ver.2.5    2026-09-24</x:v>
+      </x:c>
+      <x:c r="J2" s="55" t="str"/>
+      <x:c r="K2" s="55" t="str"/>
+      <x:c r="L2" s="55" t="str"/>
+      <x:c r="M2" s="55" t="str"/>
+      <x:c r="N2" s="55" t="str"/>
+      <x:c r="O2" s="55" t="str"/>
+      <x:c r="P2" s="55" t="str"/>
     </x:row>
     <x:row r="3" ht="21" customHeight="1">
       <x:c r="A3" s="48"/>
@@ -5595,101 +4953,39 @@
       <x:c r="A4" s="72" t="str">
         <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
       </x:c>
-      <x:c r="B4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="C4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="D4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="E4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="F4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="G4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="H4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="I4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="J4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="K4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="L4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="M4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="N4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="O4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="P4" s="74" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
+      <x:c r="B4" s="73" t="str"/>
+      <x:c r="C4" s="73" t="str"/>
+      <x:c r="D4" s="73" t="str"/>
+      <x:c r="E4" s="73" t="str"/>
+      <x:c r="F4" s="73" t="str"/>
+      <x:c r="G4" s="73" t="str"/>
+      <x:c r="H4" s="73" t="str"/>
+      <x:c r="I4" s="73" t="str"/>
+      <x:c r="J4" s="73" t="str"/>
+      <x:c r="K4" s="73" t="str"/>
+      <x:c r="L4" s="73" t="str"/>
+      <x:c r="M4" s="73" t="str"/>
+      <x:c r="N4" s="73" t="str"/>
+      <x:c r="O4" s="73" t="str"/>
+      <x:c r="P4" s="74" t="str"/>
     </x:row>
     <x:row r="5" ht="21" customHeight="1">
-      <x:c r="A5" s="75" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="B5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="C5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="D5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="E5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="F5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="G5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="H5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="I5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="J5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="K5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="L5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="M5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="N5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="O5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="P5" s="77" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
+      <x:c r="A5" s="75" t="str"/>
+      <x:c r="B5" s="76" t="str"/>
+      <x:c r="C5" s="76" t="str"/>
+      <x:c r="D5" s="76" t="str"/>
+      <x:c r="E5" s="76" t="str"/>
+      <x:c r="F5" s="76" t="str"/>
+      <x:c r="G5" s="76" t="str"/>
+      <x:c r="H5" s="76" t="str"/>
+      <x:c r="I5" s="76" t="str"/>
+      <x:c r="J5" s="76" t="str"/>
+      <x:c r="K5" s="76" t="str"/>
+      <x:c r="L5" s="76" t="str"/>
+      <x:c r="M5" s="76" t="str"/>
+      <x:c r="N5" s="76" t="str"/>
+      <x:c r="O5" s="76" t="str"/>
+      <x:c r="P5" s="77" t="str"/>
     </x:row>
     <x:row r="6" ht="21" customHeight="1">
       <x:c r="A6" s="107" t="str">
@@ -5701,218 +4997,68 @@
 通知
 System</x:v>
       </x:c>
-      <x:c r="B6" s="108" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C6" s="109" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="B6" s="108" t="str"/>
+      <x:c r="C6" s="109" t="str"/>
       <x:c r="D6" s="118" t="str">
         <x:v>Home  &gt;  ユーザー管理</x:v>
       </x:c>
-      <x:c r="E6" s="118" t="str">
-        <x:v>Home  &gt;  ユーザー管理</x:v>
-      </x:c>
-      <x:c r="F6" s="118" t="str">
-        <x:v>Home  &gt;  ユーザー管理</x:v>
-      </x:c>
-      <x:c r="G6" s="118" t="str">
-        <x:v>Home  &gt;  ユーザー管理</x:v>
-      </x:c>
-      <x:c r="H6" s="118" t="str">
-        <x:v>Home  &gt;  ユーザー管理</x:v>
-      </x:c>
-      <x:c r="I6" s="118" t="str">
-        <x:v>Home  &gt;  ユーザー管理</x:v>
-      </x:c>
-      <x:c r="J6" s="118" t="str">
-        <x:v>Home  &gt;  ユーザー管理</x:v>
-      </x:c>
-      <x:c r="K6" s="118" t="str">
-        <x:v>Home  &gt;  ユーザー管理</x:v>
-      </x:c>
-      <x:c r="L6" s="118" t="str">
-        <x:v>Home  &gt;  ユーザー管理</x:v>
-      </x:c>
-      <x:c r="M6" s="118" t="str">
-        <x:v>Home  &gt;  ユーザー管理</x:v>
-      </x:c>
-      <x:c r="N6" s="118" t="str">
-        <x:v>Home  &gt;  ユーザー管理</x:v>
-      </x:c>
-      <x:c r="O6" s="118" t="str">
-        <x:v>Home  &gt;  ユーザー管理</x:v>
-      </x:c>
-      <x:c r="P6" s="118" t="str">
-        <x:v>Home  &gt;  ユーザー管理</x:v>
-      </x:c>
+      <x:c r="E6" s="118" t="str"/>
+      <x:c r="F6" s="118" t="str"/>
+      <x:c r="G6" s="118" t="str"/>
+      <x:c r="H6" s="118" t="str"/>
+      <x:c r="I6" s="118" t="str"/>
+      <x:c r="J6" s="118" t="str"/>
+      <x:c r="K6" s="118" t="str"/>
+      <x:c r="L6" s="118" t="str"/>
+      <x:c r="M6" s="118" t="str"/>
+      <x:c r="N6" s="118" t="str"/>
+      <x:c r="O6" s="118" t="str"/>
+      <x:c r="P6" s="118" t="str"/>
     </x:row>
     <x:row r="7" ht="21" customHeight="1">
-      <x:c r="A7" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B7" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C7" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A7" s="110" t="str"/>
+      <x:c r="B7" s="111" t="str"/>
+      <x:c r="C7" s="112" t="str"/>
       <x:c r="D7" s="120" t="str">
         <x:v>ユーザー管理</x:v>
       </x:c>
-      <x:c r="E7" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="F7" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="G7" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="H7" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="I7" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="J7" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="K7" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="L7" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
+      <x:c r="E7" s="120" t="str"/>
+      <x:c r="F7" s="120" t="str"/>
+      <x:c r="G7" s="120" t="str"/>
+      <x:c r="H7" s="120" t="str"/>
+      <x:c r="I7" s="120" t="str"/>
+      <x:c r="J7" s="120" t="str"/>
+      <x:c r="K7" s="120" t="str"/>
+      <x:c r="L7" s="120" t="str"/>
       <x:c r="M7" s="48"/>
       <x:c r="N7" s="48"/>
       <x:c r="O7" s="48"/>
       <x:c r="P7" s="48"/>
     </x:row>
     <x:row r="8" ht="21" customHeight="1">
-      <x:c r="A8" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B8" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C8" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D8" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="E8" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="F8" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="G8" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="H8" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="I8" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="J8" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="K8" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
-      <x:c r="L8" s="120" t="str">
-        <x:v>ユーザー管理</x:v>
-      </x:c>
+      <x:c r="A8" s="110" t="str"/>
+      <x:c r="B8" s="111" t="str"/>
+      <x:c r="C8" s="112" t="str"/>
+      <x:c r="D8" s="120" t="str"/>
+      <x:c r="E8" s="120" t="str"/>
+      <x:c r="F8" s="120" t="str"/>
+      <x:c r="G8" s="120" t="str"/>
+      <x:c r="H8" s="120" t="str"/>
+      <x:c r="I8" s="120" t="str"/>
+      <x:c r="J8" s="120" t="str"/>
+      <x:c r="K8" s="120" t="str"/>
+      <x:c r="L8" s="120" t="str"/>
       <x:c r="M8" s="48"/>
       <x:c r="N8" s="143" t="str">
         <x:v>新規</x:v>
       </x:c>
-      <x:c r="O8" s="144" t="str">
-        <x:v>新規</x:v>
-      </x:c>
-      <x:c r="P8" s="145" t="str">
-        <x:v>新規</x:v>
-      </x:c>
+      <x:c r="O8" s="144" t="str"/>
+      <x:c r="P8" s="145" t="str"/>
     </x:row>
     <x:row r="9" ht="21" customHeight="1">
-      <x:c r="A9" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B9" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C9" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A9" s="110" t="str"/>
+      <x:c r="B9" s="111" t="str"/>
+      <x:c r="C9" s="112" t="str"/>
       <x:c r="D9" s="48"/>
       <x:c r="E9" s="48"/>
       <x:c r="F9" s="48"/>
@@ -5928,159 +5074,55 @@
       <x:c r="P9" s="48"/>
     </x:row>
     <x:row r="10" ht="21" customHeight="1">
-      <x:c r="A10" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B10" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C10" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A10" s="110" t="str"/>
+      <x:c r="B10" s="111" t="str"/>
+      <x:c r="C10" s="112" t="str"/>
       <x:c r="D10" s="122" t="str">
         <x:v>検索条件</x:v>
       </x:c>
-      <x:c r="E10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="F10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="G10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="H10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="I10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="J10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="K10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="L10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="M10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="N10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="O10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="P10" s="124" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
+      <x:c r="E10" s="123" t="str"/>
+      <x:c r="F10" s="123" t="str"/>
+      <x:c r="G10" s="123" t="str"/>
+      <x:c r="H10" s="123" t="str"/>
+      <x:c r="I10" s="123" t="str"/>
+      <x:c r="J10" s="123" t="str"/>
+      <x:c r="K10" s="123" t="str"/>
+      <x:c r="L10" s="123" t="str"/>
+      <x:c r="M10" s="123" t="str"/>
+      <x:c r="N10" s="123" t="str"/>
+      <x:c r="O10" s="123" t="str"/>
+      <x:c r="P10" s="124" t="str"/>
     </x:row>
     <x:row r="11" ht="21" customHeight="1">
-      <x:c r="A11" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B11" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C11" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A11" s="110" t="str"/>
+      <x:c r="B11" s="111" t="str"/>
+      <x:c r="C11" s="112" t="str"/>
       <x:c r="D11" s="126" t="str">
         <x:v>ユーザー名</x:v>
       </x:c>
-      <x:c r="E11" s="126" t="str">
-        <x:v>ユーザー名</x:v>
-      </x:c>
+      <x:c r="E11" s="126" t="str"/>
       <x:c r="F11" s="129" t="str"/>
       <x:c r="G11" s="129" t="str"/>
       <x:c r="H11" s="126" t="str">
         <x:v>社員</x:v>
       </x:c>
-      <x:c r="I11" s="126" t="str">
-        <x:v>社員</x:v>
-      </x:c>
+      <x:c r="I11" s="126" t="str"/>
       <x:c r="J11" s="129" t="str"/>
       <x:c r="K11" s="129" t="str"/>
       <x:c r="L11" s="126" t="str">
         <x:v>状態</x:v>
       </x:c>
-      <x:c r="M11" s="126" t="str">
-        <x:v>状態</x:v>
-      </x:c>
+      <x:c r="M11" s="126" t="str"/>
       <x:c r="N11" s="129" t="str">
         <x:v>すべて  ▼</x:v>
       </x:c>
-      <x:c r="O11" s="129" t="str">
-        <x:v>すべて  ▼</x:v>
-      </x:c>
+      <x:c r="O11" s="129" t="str"/>
       <x:c r="P11" s="48"/>
     </x:row>
     <x:row r="12" ht="21" customHeight="1">
-      <x:c r="A12" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B12" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C12" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A12" s="110" t="str"/>
+      <x:c r="B12" s="111" t="str"/>
+      <x:c r="C12" s="112" t="str"/>
       <x:c r="D12" s="48"/>
       <x:c r="E12" s="48"/>
       <x:c r="F12" s="48"/>
@@ -6096,33 +5138,9 @@
       <x:c r="P12" s="48"/>
     </x:row>
     <x:row r="13" ht="21" customHeight="1">
-      <x:c r="A13" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B13" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C13" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A13" s="110" t="str"/>
+      <x:c r="B13" s="111" t="str"/>
+      <x:c r="C13" s="112" t="str"/>
       <x:c r="D13" s="48"/>
       <x:c r="E13" s="48"/>
       <x:c r="F13" s="48"/>
@@ -6138,33 +5156,9 @@
       <x:c r="P13" s="48"/>
     </x:row>
     <x:row r="14" ht="21" customHeight="1">
-      <x:c r="A14" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B14" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C14" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A14" s="110" t="str"/>
+      <x:c r="B14" s="111" t="str"/>
+      <x:c r="C14" s="112" t="str"/>
       <x:c r="D14" s="48"/>
       <x:c r="E14" s="48"/>
       <x:c r="F14" s="48"/>
@@ -6180,33 +5174,9 @@
       <x:c r="P14" s="48"/>
     </x:row>
     <x:row r="15" ht="21" customHeight="1">
-      <x:c r="A15" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B15" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C15" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A15" s="110" t="str"/>
+      <x:c r="B15" s="111" t="str"/>
+      <x:c r="C15" s="112" t="str"/>
       <x:c r="D15" s="48"/>
       <x:c r="E15" s="48"/>
       <x:c r="F15" s="48"/>
@@ -6218,47 +5188,17 @@
       <x:c r="L15" s="135" t="str">
         <x:v>クリア</x:v>
       </x:c>
-      <x:c r="M15" s="136" t="str">
-        <x:v>クリア</x:v>
-      </x:c>
+      <x:c r="M15" s="136" t="str"/>
       <x:c r="N15" s="143" t="str">
         <x:v>検索</x:v>
       </x:c>
-      <x:c r="O15" s="144" t="str">
-        <x:v>検索</x:v>
-      </x:c>
-      <x:c r="P15" s="145" t="str">
-        <x:v>検索</x:v>
-      </x:c>
+      <x:c r="O15" s="144" t="str"/>
+      <x:c r="P15" s="145" t="str"/>
     </x:row>
     <x:row r="16" ht="21" customHeight="1">
-      <x:c r="A16" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B16" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C16" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A16" s="110" t="str"/>
+      <x:c r="B16" s="111" t="str"/>
+      <x:c r="C16" s="112" t="str"/>
       <x:c r="D16" s="48"/>
       <x:c r="E16" s="48"/>
       <x:c r="F16" s="48"/>
@@ -6274,305 +5214,137 @@
       <x:c r="P16" s="48"/>
     </x:row>
     <x:row r="17" ht="21" customHeight="1">
-      <x:c r="A17" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B17" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C17" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A17" s="110" t="str"/>
+      <x:c r="B17" s="111" t="str"/>
+      <x:c r="C17" s="112" t="str"/>
       <x:c r="D17" s="150" t="str">
         <x:v>ユーザー名</x:v>
       </x:c>
-      <x:c r="E17" s="150" t="str">
-        <x:v>ユーザー名</x:v>
-      </x:c>
+      <x:c r="E17" s="150" t="str"/>
       <x:c r="F17" s="150" t="str">
         <x:v>社員</x:v>
       </x:c>
-      <x:c r="G17" s="150" t="str">
-        <x:v>社員</x:v>
-      </x:c>
+      <x:c r="G17" s="150" t="str"/>
       <x:c r="H17" s="150" t="str">
         <x:v>Role</x:v>
       </x:c>
-      <x:c r="I17" s="150" t="str">
-        <x:v>Role</x:v>
-      </x:c>
+      <x:c r="I17" s="150" t="str"/>
       <x:c r="J17" s="150" t="str">
         <x:v>状態</x:v>
       </x:c>
-      <x:c r="K17" s="150" t="str">
-        <x:v>状態</x:v>
-      </x:c>
+      <x:c r="K17" s="150" t="str"/>
       <x:c r="L17" s="150" t="str">
         <x:v>失敗回数</x:v>
       </x:c>
-      <x:c r="M17" s="150" t="str">
-        <x:v>失敗回数</x:v>
-      </x:c>
+      <x:c r="M17" s="150" t="str"/>
       <x:c r="N17" s="150" t="str">
         <x:v>最終Login</x:v>
       </x:c>
-      <x:c r="O17" s="150" t="str">
-        <x:v>最終Login</x:v>
-      </x:c>
+      <x:c r="O17" s="150" t="str"/>
       <x:c r="P17" s="150" t="str">
         <x:v>操作</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="21" customHeight="1">
-      <x:c r="A18" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B18" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C18" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A18" s="110" t="str"/>
+      <x:c r="B18" s="111" t="str"/>
+      <x:c r="C18" s="112" t="str"/>
       <x:c r="D18" s="154" t="str">
         <x:v>サンプル1</x:v>
       </x:c>
-      <x:c r="E18" s="154" t="str">
-        <x:v>サンプル1</x:v>
-      </x:c>
+      <x:c r="E18" s="154" t="str"/>
       <x:c r="F18" s="154" t="str">
         <x:v>サンプル1</x:v>
       </x:c>
-      <x:c r="G18" s="154" t="str">
-        <x:v>サンプル1</x:v>
-      </x:c>
+      <x:c r="G18" s="154" t="str"/>
       <x:c r="H18" s="154" t="str">
         <x:v>サンプル1</x:v>
       </x:c>
-      <x:c r="I18" s="154" t="str">
-        <x:v>サンプル1</x:v>
-      </x:c>
+      <x:c r="I18" s="154" t="str"/>
       <x:c r="J18" s="154" t="str">
         <x:v>ACTIVE</x:v>
       </x:c>
-      <x:c r="K18" s="154" t="str">
-        <x:v>ACTIVE</x:v>
-      </x:c>
+      <x:c r="K18" s="154" t="str"/>
       <x:c r="L18" s="154" t="str">
         <x:v>サンプル1</x:v>
       </x:c>
-      <x:c r="M18" s="154" t="str">
-        <x:v>サンプル1</x:v>
-      </x:c>
+      <x:c r="M18" s="154" t="str"/>
       <x:c r="N18" s="154" t="str">
         <x:v>2026-08-01</x:v>
       </x:c>
-      <x:c r="O18" s="154" t="str">
-        <x:v>2026-08-01</x:v>
-      </x:c>
+      <x:c r="O18" s="154" t="str"/>
       <x:c r="P18" s="160" t="str">
         <x:v>詳細</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="21" customHeight="1">
-      <x:c r="A19" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B19" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C19" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A19" s="110" t="str"/>
+      <x:c r="B19" s="111" t="str"/>
+      <x:c r="C19" s="112" t="str"/>
       <x:c r="D19" s="158" t="str">
         <x:v>サンプル2</x:v>
       </x:c>
-      <x:c r="E19" s="158" t="str">
-        <x:v>サンプル2</x:v>
-      </x:c>
+      <x:c r="E19" s="158" t="str"/>
       <x:c r="F19" s="158" t="str">
         <x:v>サンプル2</x:v>
       </x:c>
-      <x:c r="G19" s="158" t="str">
-        <x:v>サンプル2</x:v>
-      </x:c>
+      <x:c r="G19" s="158" t="str"/>
       <x:c r="H19" s="158" t="str">
         <x:v>サンプル2</x:v>
       </x:c>
-      <x:c r="I19" s="158" t="str">
-        <x:v>サンプル2</x:v>
-      </x:c>
+      <x:c r="I19" s="158" t="str"/>
       <x:c r="J19" s="158" t="str">
-        <x:v>IN_PROGRESS</x:v>
-      </x:c>
-      <x:c r="K19" s="158" t="str">
-        <x:v>IN_PROGRESS</x:v>
-      </x:c>
+        <x:v>DISABLED</x:v>
+      </x:c>
+      <x:c r="K19" s="158" t="str"/>
       <x:c r="L19" s="158" t="str">
         <x:v>サンプル2</x:v>
       </x:c>
-      <x:c r="M19" s="158" t="str">
-        <x:v>サンプル2</x:v>
-      </x:c>
+      <x:c r="M19" s="158" t="str"/>
       <x:c r="N19" s="158" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
-      <x:c r="O19" s="158" t="str">
-        <x:v>2026-08-02</x:v>
-      </x:c>
+      <x:c r="O19" s="158" t="str"/>
       <x:c r="P19" s="162" t="str">
         <x:v>詳細</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="21" customHeight="1">
-      <x:c r="A20" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B20" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C20" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A20" s="110" t="str"/>
+      <x:c r="B20" s="111" t="str"/>
+      <x:c r="C20" s="112" t="str"/>
       <x:c r="D20" s="154" t="str">
         <x:v>サンプル3</x:v>
       </x:c>
-      <x:c r="E20" s="154" t="str">
-        <x:v>サンプル3</x:v>
-      </x:c>
+      <x:c r="E20" s="154" t="str"/>
       <x:c r="F20" s="154" t="str">
         <x:v>サンプル3</x:v>
       </x:c>
-      <x:c r="G20" s="154" t="str">
-        <x:v>サンプル3</x:v>
-      </x:c>
+      <x:c r="G20" s="154" t="str"/>
       <x:c r="H20" s="154" t="str">
         <x:v>サンプル3</x:v>
       </x:c>
-      <x:c r="I20" s="154" t="str">
-        <x:v>サンプル3</x:v>
-      </x:c>
+      <x:c r="I20" s="154" t="str"/>
       <x:c r="J20" s="154" t="str">
-        <x:v>IN_PROGRESS</x:v>
-      </x:c>
-      <x:c r="K20" s="154" t="str">
-        <x:v>IN_PROGRESS</x:v>
-      </x:c>
+        <x:v>LOCKED</x:v>
+      </x:c>
+      <x:c r="K20" s="154" t="str"/>
       <x:c r="L20" s="154" t="str">
         <x:v>サンプル3</x:v>
       </x:c>
-      <x:c r="M20" s="154" t="str">
-        <x:v>サンプル3</x:v>
-      </x:c>
+      <x:c r="M20" s="154" t="str"/>
       <x:c r="N20" s="154" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
-      <x:c r="O20" s="154" t="str">
-        <x:v>2026-08-03</x:v>
-      </x:c>
+      <x:c r="O20" s="154" t="str"/>
       <x:c r="P20" s="160" t="str">
         <x:v>詳細</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="21" customHeight="1">
-      <x:c r="A21" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B21" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C21" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A21" s="110" t="str"/>
+      <x:c r="B21" s="111" t="str"/>
+      <x:c r="C21" s="112" t="str"/>
       <x:c r="D21" s="158" t="str"/>
       <x:c r="E21" s="158" t="str"/>
       <x:c r="F21" s="158" t="str"/>
@@ -6588,33 +5360,9 @@
       <x:c r="P21" s="162" t="str"/>
     </x:row>
     <x:row r="22" ht="21" customHeight="1">
-      <x:c r="A22" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B22" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C22" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A22" s="110" t="str"/>
+      <x:c r="B22" s="111" t="str"/>
+      <x:c r="C22" s="112" t="str"/>
       <x:c r="D22" s="154" t="str"/>
       <x:c r="E22" s="154" t="str"/>
       <x:c r="F22" s="154" t="str"/>
@@ -6630,33 +5378,9 @@
       <x:c r="P22" s="160" t="str"/>
     </x:row>
     <x:row r="23" ht="21" customHeight="1">
-      <x:c r="A23" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B23" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C23" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A23" s="110" t="str"/>
+      <x:c r="B23" s="111" t="str"/>
+      <x:c r="C23" s="112" t="str"/>
       <x:c r="D23" s="158" t="str"/>
       <x:c r="E23" s="158" t="str"/>
       <x:c r="F23" s="158" t="str"/>
@@ -6672,33 +5396,9 @@
       <x:c r="P23" s="162" t="str"/>
     </x:row>
     <x:row r="24" ht="21" customHeight="1">
-      <x:c r="A24" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B24" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C24" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A24" s="110" t="str"/>
+      <x:c r="B24" s="111" t="str"/>
+      <x:c r="C24" s="112" t="str"/>
       <x:c r="D24" s="48"/>
       <x:c r="E24" s="48"/>
       <x:c r="F24" s="48"/>
@@ -6714,95 +5414,33 @@
       <x:c r="P24" s="48"/>
     </x:row>
     <x:row r="25" ht="21" customHeight="1">
-      <x:c r="A25" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B25" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C25" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A25" s="110" t="str"/>
+      <x:c r="B25" s="111" t="str"/>
+      <x:c r="C25" s="112" t="str"/>
       <x:c r="D25" s="163" t="str">
         <x:v>1-20 / 128件</x:v>
       </x:c>
-      <x:c r="E25" s="163" t="str">
-        <x:v>1-20 / 128件</x:v>
-      </x:c>
-      <x:c r="F25" s="163" t="str">
-        <x:v>1-20 / 128件</x:v>
-      </x:c>
-      <x:c r="G25" s="163" t="str">
-        <x:v>1-20 / 128件</x:v>
-      </x:c>
-      <x:c r="H25" s="163" t="str">
-        <x:v>1-20 / 128件</x:v>
-      </x:c>
+      <x:c r="E25" s="163" t="str"/>
+      <x:c r="F25" s="163" t="str"/>
+      <x:c r="G25" s="163" t="str"/>
+      <x:c r="H25" s="163" t="str"/>
       <x:c r="I25" s="48"/>
       <x:c r="J25" s="48"/>
       <x:c r="K25" s="48"/>
       <x:c r="L25" s="135" t="str">
         <x:v>&lt; 前へ</x:v>
       </x:c>
-      <x:c r="M25" s="136" t="str">
-        <x:v>&lt; 前へ</x:v>
-      </x:c>
+      <x:c r="M25" s="136" t="str"/>
       <x:c r="N25" s="135" t="str">
         <x:v>次へ &gt;</x:v>
       </x:c>
-      <x:c r="O25" s="166" t="str">
-        <x:v>次へ &gt;</x:v>
-      </x:c>
-      <x:c r="P25" s="136" t="str">
-        <x:v>次へ &gt;</x:v>
-      </x:c>
+      <x:c r="O25" s="166" t="str"/>
+      <x:c r="P25" s="136" t="str"/>
     </x:row>
     <x:row r="26" ht="21" customHeight="1">
-      <x:c r="A26" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B26" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C26" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A26" s="110" t="str"/>
+      <x:c r="B26" s="111" t="str"/>
+      <x:c r="C26" s="112" t="str"/>
       <x:c r="D26" s="48"/>
       <x:c r="E26" s="48"/>
       <x:c r="F26" s="48"/>
@@ -6818,33 +5456,9 @@
       <x:c r="P26" s="48"/>
     </x:row>
     <x:row r="27" ht="21" customHeight="1">
-      <x:c r="A27" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B27" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C27" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A27" s="110" t="str"/>
+      <x:c r="B27" s="111" t="str"/>
+      <x:c r="C27" s="112" t="str"/>
       <x:c r="D27" s="48"/>
       <x:c r="E27" s="48"/>
       <x:c r="F27" s="48"/>
@@ -6860,33 +5474,9 @@
       <x:c r="P27" s="48"/>
     </x:row>
     <x:row r="28" ht="21" customHeight="1">
-      <x:c r="A28" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B28" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C28" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A28" s="110" t="str"/>
+      <x:c r="B28" s="111" t="str"/>
+      <x:c r="C28" s="112" t="str"/>
       <x:c r="D28" s="48"/>
       <x:c r="E28" s="48"/>
       <x:c r="F28" s="48"/>
@@ -6902,33 +5492,9 @@
       <x:c r="P28" s="48"/>
     </x:row>
     <x:row r="29" ht="21" customHeight="1">
-      <x:c r="A29" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B29" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C29" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A29" s="110" t="str"/>
+      <x:c r="B29" s="111" t="str"/>
+      <x:c r="C29" s="112" t="str"/>
       <x:c r="D29" s="48"/>
       <x:c r="E29" s="48"/>
       <x:c r="F29" s="48"/>
@@ -6944,33 +5510,9 @@
       <x:c r="P29" s="48"/>
     </x:row>
     <x:row r="30" ht="21" customHeight="1">
-      <x:c r="A30" s="113" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B30" s="114" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C30" s="115" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A30" s="113" t="str"/>
+      <x:c r="B30" s="114" t="str"/>
+      <x:c r="C30" s="115" t="str"/>
       <x:c r="D30" s="48"/>
       <x:c r="E30" s="48"/>
       <x:c r="F30" s="48"/>
@@ -7091,7 +5633,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -7117,101 +5659,43 @@
       <x:c r="A1" s="52" t="str">
         <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
       </x:c>
-      <x:c r="B1" s="52" t="str">
-        <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="C1" s="52" t="str">
-        <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="D1" s="52" t="str">
-        <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="E1" s="52" t="str">
-        <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="F1" s="52" t="str">
-        <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="G1" s="52" t="str">
-        <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="H1" s="52" t="str">
-        <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="I1" s="52" t="str">
-        <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="J1" s="52" t="str">
-        <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="K1" s="52" t="str">
-        <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="L1" s="52" t="str">
-        <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="M1" s="52" t="str">
-        <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="N1" s="52" t="str">
-        <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="O1" s="52" t="str">
-        <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="P1" s="52" t="str">
-        <x:v>SCR-024  ロール管理  画面レイアウト</x:v>
-      </x:c>
+      <x:c r="B1" s="52" t="str"/>
+      <x:c r="C1" s="52" t="str"/>
+      <x:c r="D1" s="52" t="str"/>
+      <x:c r="E1" s="52" t="str"/>
+      <x:c r="F1" s="52" t="str"/>
+      <x:c r="G1" s="52" t="str"/>
+      <x:c r="H1" s="52" t="str"/>
+      <x:c r="I1" s="52" t="str"/>
+      <x:c r="J1" s="52" t="str"/>
+      <x:c r="K1" s="52" t="str"/>
+      <x:c r="L1" s="52" t="str"/>
+      <x:c r="M1" s="52" t="str"/>
+      <x:c r="N1" s="52" t="str"/>
+      <x:c r="O1" s="52" t="str"/>
+      <x:c r="P1" s="52" t="str"/>
     </x:row>
     <x:row r="2" ht="21" customHeight="1">
       <x:c r="A2" s="54" t="str">
         <x:v>画面ID: SCR-024    画面名: ロール管理</x:v>
       </x:c>
-      <x:c r="B2" s="54" t="str">
-        <x:v>画面ID: SCR-024    画面名: ロール管理</x:v>
-      </x:c>
-      <x:c r="C2" s="54" t="str">
-        <x:v>画面ID: SCR-024    画面名: ロール管理</x:v>
-      </x:c>
-      <x:c r="D2" s="54" t="str">
-        <x:v>画面ID: SCR-024    画面名: ロール管理</x:v>
-      </x:c>
-      <x:c r="E2" s="54" t="str">
-        <x:v>画面ID: SCR-024    画面名: ロール管理</x:v>
-      </x:c>
-      <x:c r="F2" s="54" t="str">
-        <x:v>画面ID: SCR-024    画面名: ロール管理</x:v>
-      </x:c>
-      <x:c r="G2" s="54" t="str">
-        <x:v>画面ID: SCR-024    画面名: ロール管理</x:v>
-      </x:c>
-      <x:c r="H2" s="54" t="str">
-        <x:v>画面ID: SCR-024    画面名: ロール管理</x:v>
-      </x:c>
-      <x:c r="I2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="J2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="K2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="L2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="M2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="N2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="O2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="P2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
+      <x:c r="B2" s="54" t="str"/>
+      <x:c r="C2" s="54" t="str"/>
+      <x:c r="D2" s="54" t="str"/>
+      <x:c r="E2" s="54" t="str"/>
+      <x:c r="F2" s="54" t="str"/>
+      <x:c r="G2" s="54" t="str"/>
+      <x:c r="H2" s="54" t="str"/>
+      <x:c r="I2" s="370" t="str">
+        <x:v>Ver.2.5    2026-09-24</x:v>
+      </x:c>
+      <x:c r="J2" s="55" t="str"/>
+      <x:c r="K2" s="55" t="str"/>
+      <x:c r="L2" s="55" t="str"/>
+      <x:c r="M2" s="55" t="str"/>
+      <x:c r="N2" s="55" t="str"/>
+      <x:c r="O2" s="55" t="str"/>
+      <x:c r="P2" s="55" t="str"/>
     </x:row>
     <x:row r="3" ht="21" customHeight="1">
       <x:c r="A3" s="48"/>
@@ -7235,101 +5719,39 @@
       <x:c r="A4" s="72" t="str">
         <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
       </x:c>
-      <x:c r="B4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="C4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="D4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="E4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="F4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="G4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="H4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="I4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="J4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="K4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="L4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="M4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="N4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="O4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="P4" s="74" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
+      <x:c r="B4" s="73" t="str"/>
+      <x:c r="C4" s="73" t="str"/>
+      <x:c r="D4" s="73" t="str"/>
+      <x:c r="E4" s="73" t="str"/>
+      <x:c r="F4" s="73" t="str"/>
+      <x:c r="G4" s="73" t="str"/>
+      <x:c r="H4" s="73" t="str"/>
+      <x:c r="I4" s="73" t="str"/>
+      <x:c r="J4" s="73" t="str"/>
+      <x:c r="K4" s="73" t="str"/>
+      <x:c r="L4" s="73" t="str"/>
+      <x:c r="M4" s="73" t="str"/>
+      <x:c r="N4" s="73" t="str"/>
+      <x:c r="O4" s="73" t="str"/>
+      <x:c r="P4" s="74" t="str"/>
     </x:row>
     <x:row r="5" ht="21" customHeight="1">
-      <x:c r="A5" s="75" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="B5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="C5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="D5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="E5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="F5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="G5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="H5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="I5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="J5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="K5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="L5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="M5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="N5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="O5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="P5" s="77" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
+      <x:c r="A5" s="75" t="str"/>
+      <x:c r="B5" s="76" t="str"/>
+      <x:c r="C5" s="76" t="str"/>
+      <x:c r="D5" s="76" t="str"/>
+      <x:c r="E5" s="76" t="str"/>
+      <x:c r="F5" s="76" t="str"/>
+      <x:c r="G5" s="76" t="str"/>
+      <x:c r="H5" s="76" t="str"/>
+      <x:c r="I5" s="76" t="str"/>
+      <x:c r="J5" s="76" t="str"/>
+      <x:c r="K5" s="76" t="str"/>
+      <x:c r="L5" s="76" t="str"/>
+      <x:c r="M5" s="76" t="str"/>
+      <x:c r="N5" s="76" t="str"/>
+      <x:c r="O5" s="76" t="str"/>
+      <x:c r="P5" s="77" t="str"/>
     </x:row>
     <x:row r="6" ht="21" customHeight="1">
       <x:c r="A6" s="107" t="str">
@@ -7341,212 +5763,66 @@
 通知
 System</x:v>
       </x:c>
-      <x:c r="B6" s="108" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C6" s="109" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="B6" s="108" t="str"/>
+      <x:c r="C6" s="109" t="str"/>
       <x:c r="D6" s="118" t="str">
         <x:v>Home  &gt;  ロール管理</x:v>
       </x:c>
-      <x:c r="E6" s="118" t="str">
-        <x:v>Home  &gt;  ロール管理</x:v>
-      </x:c>
-      <x:c r="F6" s="118" t="str">
-        <x:v>Home  &gt;  ロール管理</x:v>
-      </x:c>
-      <x:c r="G6" s="118" t="str">
-        <x:v>Home  &gt;  ロール管理</x:v>
-      </x:c>
-      <x:c r="H6" s="118" t="str">
-        <x:v>Home  &gt;  ロール管理</x:v>
-      </x:c>
-      <x:c r="I6" s="118" t="str">
-        <x:v>Home  &gt;  ロール管理</x:v>
-      </x:c>
-      <x:c r="J6" s="118" t="str">
-        <x:v>Home  &gt;  ロール管理</x:v>
-      </x:c>
-      <x:c r="K6" s="118" t="str">
-        <x:v>Home  &gt;  ロール管理</x:v>
-      </x:c>
-      <x:c r="L6" s="118" t="str">
-        <x:v>Home  &gt;  ロール管理</x:v>
-      </x:c>
-      <x:c r="M6" s="118" t="str">
-        <x:v>Home  &gt;  ロール管理</x:v>
-      </x:c>
-      <x:c r="N6" s="118" t="str">
-        <x:v>Home  &gt;  ロール管理</x:v>
-      </x:c>
-      <x:c r="O6" s="118" t="str">
-        <x:v>Home  &gt;  ロール管理</x:v>
-      </x:c>
-      <x:c r="P6" s="118" t="str">
-        <x:v>Home  &gt;  ロール管理</x:v>
-      </x:c>
+      <x:c r="E6" s="118" t="str"/>
+      <x:c r="F6" s="118" t="str"/>
+      <x:c r="G6" s="118" t="str"/>
+      <x:c r="H6" s="118" t="str"/>
+      <x:c r="I6" s="118" t="str"/>
+      <x:c r="J6" s="118" t="str"/>
+      <x:c r="K6" s="118" t="str"/>
+      <x:c r="L6" s="118" t="str"/>
+      <x:c r="M6" s="118" t="str"/>
+      <x:c r="N6" s="118" t="str"/>
+      <x:c r="O6" s="118" t="str"/>
+      <x:c r="P6" s="118" t="str"/>
     </x:row>
     <x:row r="7" ht="21" customHeight="1">
-      <x:c r="A7" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B7" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C7" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A7" s="110" t="str"/>
+      <x:c r="B7" s="111" t="str"/>
+      <x:c r="C7" s="112" t="str"/>
       <x:c r="D7" s="120" t="str">
         <x:v>ロール管理</x:v>
       </x:c>
-      <x:c r="E7" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="F7" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="G7" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="H7" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="I7" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="J7" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="K7" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="L7" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
+      <x:c r="E7" s="120" t="str"/>
+      <x:c r="F7" s="120" t="str"/>
+      <x:c r="G7" s="120" t="str"/>
+      <x:c r="H7" s="120" t="str"/>
+      <x:c r="I7" s="120" t="str"/>
+      <x:c r="J7" s="120" t="str"/>
+      <x:c r="K7" s="120" t="str"/>
+      <x:c r="L7" s="120" t="str"/>
       <x:c r="M7" s="48"/>
       <x:c r="N7" s="48"/>
       <x:c r="O7" s="48"/>
       <x:c r="P7" s="48"/>
     </x:row>
     <x:row r="8" ht="21" customHeight="1">
-      <x:c r="A8" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B8" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C8" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D8" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="E8" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="F8" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="G8" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="H8" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="I8" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="J8" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="K8" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
-      <x:c r="L8" s="120" t="str">
-        <x:v>ロール管理</x:v>
-      </x:c>
+      <x:c r="A8" s="110" t="str"/>
+      <x:c r="B8" s="111" t="str"/>
+      <x:c r="C8" s="112" t="str"/>
+      <x:c r="D8" s="120" t="str"/>
+      <x:c r="E8" s="120" t="str"/>
+      <x:c r="F8" s="120" t="str"/>
+      <x:c r="G8" s="120" t="str"/>
+      <x:c r="H8" s="120" t="str"/>
+      <x:c r="I8" s="120" t="str"/>
+      <x:c r="J8" s="120" t="str"/>
+      <x:c r="K8" s="120" t="str"/>
+      <x:c r="L8" s="120" t="str"/>
       <x:c r="M8" s="48"/>
       <x:c r="N8" s="48"/>
       <x:c r="O8" s="48"/>
       <x:c r="P8" s="48"/>
     </x:row>
     <x:row r="9" ht="21" customHeight="1">
-      <x:c r="A9" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B9" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C9" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A9" s="110" t="str"/>
+      <x:c r="B9" s="111" t="str"/>
+      <x:c r="C9" s="112" t="str"/>
       <x:c r="D9" s="48"/>
       <x:c r="E9" s="48"/>
       <x:c r="F9" s="48"/>
@@ -7562,169 +5838,55 @@
       <x:c r="P9" s="48"/>
     </x:row>
     <x:row r="10" ht="21" customHeight="1">
-      <x:c r="A10" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B10" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C10" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A10" s="110" t="str"/>
+      <x:c r="B10" s="111" t="str"/>
+      <x:c r="C10" s="112" t="str"/>
       <x:c r="D10" s="167" t="str">
         <x:v>Role基本情報</x:v>
       </x:c>
-      <x:c r="E10" s="168" t="str">
-        <x:v>Role基本情報</x:v>
-      </x:c>
-      <x:c r="F10" s="168" t="str">
-        <x:v>Role基本情報</x:v>
-      </x:c>
-      <x:c r="G10" s="168" t="str">
-        <x:v>Role基本情報</x:v>
-      </x:c>
-      <x:c r="H10" s="168" t="str">
-        <x:v>Role基本情報</x:v>
-      </x:c>
-      <x:c r="I10" s="168" t="str">
-        <x:v>Role基本情報</x:v>
-      </x:c>
-      <x:c r="J10" s="168" t="str">
-        <x:v>Role基本情報</x:v>
-      </x:c>
-      <x:c r="K10" s="168" t="str">
-        <x:v>Role基本情報</x:v>
-      </x:c>
-      <x:c r="L10" s="168" t="str">
-        <x:v>Role基本情報</x:v>
-      </x:c>
-      <x:c r="M10" s="168" t="str">
-        <x:v>Role基本情報</x:v>
-      </x:c>
-      <x:c r="N10" s="168" t="str">
-        <x:v>Role基本情報</x:v>
-      </x:c>
-      <x:c r="O10" s="168" t="str">
-        <x:v>Role基本情報</x:v>
-      </x:c>
-      <x:c r="P10" s="169" t="str">
-        <x:v>Role基本情報</x:v>
-      </x:c>
+      <x:c r="E10" s="168" t="str"/>
+      <x:c r="F10" s="168" t="str"/>
+      <x:c r="G10" s="168" t="str"/>
+      <x:c r="H10" s="168" t="str"/>
+      <x:c r="I10" s="168" t="str"/>
+      <x:c r="J10" s="168" t="str"/>
+      <x:c r="K10" s="168" t="str"/>
+      <x:c r="L10" s="168" t="str"/>
+      <x:c r="M10" s="168" t="str"/>
+      <x:c r="N10" s="168" t="str"/>
+      <x:c r="O10" s="168" t="str"/>
+      <x:c r="P10" s="169" t="str"/>
     </x:row>
     <x:row r="11" ht="21" customHeight="1">
-      <x:c r="A11" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B11" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C11" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A11" s="110" t="str"/>
+      <x:c r="B11" s="111" t="str"/>
+      <x:c r="C11" s="112" t="str"/>
       <x:c r="D11" s="171" t="str">
         <x:v>1. Role Code *</x:v>
       </x:c>
-      <x:c r="E11" s="171" t="str">
-        <x:v>1. Role Code *</x:v>
-      </x:c>
-      <x:c r="F11" s="171" t="str">
-        <x:v>1. Role Code *</x:v>
-      </x:c>
+      <x:c r="E11" s="171" t="str"/>
+      <x:c r="F11" s="171" t="str"/>
       <x:c r="G11" s="129" t="str">
         <x:v>PM</x:v>
       </x:c>
-      <x:c r="H11" s="129" t="str">
-        <x:v>PM</x:v>
-      </x:c>
-      <x:c r="I11" s="129" t="str">
-        <x:v>PM</x:v>
-      </x:c>
-      <x:c r="J11" s="129" t="str">
-        <x:v>PM</x:v>
-      </x:c>
+      <x:c r="H11" s="129" t="str"/>
+      <x:c r="I11" s="129" t="str"/>
+      <x:c r="J11" s="129" t="str"/>
       <x:c r="K11" s="171" t="str">
         <x:v>2. Role名 *</x:v>
       </x:c>
-      <x:c r="L11" s="171" t="str">
-        <x:v>2. Role名 *</x:v>
-      </x:c>
-      <x:c r="M11" s="171" t="str">
-        <x:v>2. Role名 *</x:v>
-      </x:c>
+      <x:c r="L11" s="171" t="str"/>
+      <x:c r="M11" s="171" t="str"/>
       <x:c r="N11" s="129" t="str">
         <x:v>Project Manager</x:v>
       </x:c>
-      <x:c r="O11" s="129" t="str">
-        <x:v>Project Manager</x:v>
-      </x:c>
-      <x:c r="P11" s="129" t="str">
-        <x:v>Project Manager</x:v>
-      </x:c>
+      <x:c r="O11" s="129" t="str"/>
+      <x:c r="P11" s="129" t="str"/>
     </x:row>
     <x:row r="12" ht="21" customHeight="1">
-      <x:c r="A12" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B12" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C12" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A12" s="110" t="str"/>
+      <x:c r="B12" s="111" t="str"/>
+      <x:c r="C12" s="112" t="str"/>
       <x:c r="D12" s="48"/>
       <x:c r="E12" s="48"/>
       <x:c r="F12" s="48"/>
@@ -7740,167 +5902,51 @@
       <x:c r="P12" s="48"/>
     </x:row>
     <x:row r="13" ht="21" customHeight="1">
-      <x:c r="A13" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B13" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C13" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A13" s="110" t="str"/>
+      <x:c r="B13" s="111" t="str"/>
+      <x:c r="C13" s="112" t="str"/>
       <x:c r="D13" s="167" t="str">
         <x:v>3. 権限一覧 *</x:v>
       </x:c>
-      <x:c r="E13" s="168" t="str">
-        <x:v>3. 権限一覧 *</x:v>
-      </x:c>
-      <x:c r="F13" s="168" t="str">
-        <x:v>3. 権限一覧 *</x:v>
-      </x:c>
-      <x:c r="G13" s="168" t="str">
-        <x:v>3. 権限一覧 *</x:v>
-      </x:c>
-      <x:c r="H13" s="168" t="str">
-        <x:v>3. 権限一覧 *</x:v>
-      </x:c>
-      <x:c r="I13" s="168" t="str">
-        <x:v>3. 権限一覧 *</x:v>
-      </x:c>
-      <x:c r="J13" s="168" t="str">
-        <x:v>3. 権限一覧 *</x:v>
-      </x:c>
-      <x:c r="K13" s="168" t="str">
-        <x:v>3. 権限一覧 *</x:v>
-      </x:c>
-      <x:c r="L13" s="168" t="str">
-        <x:v>3. 権限一覧 *</x:v>
-      </x:c>
-      <x:c r="M13" s="168" t="str">
-        <x:v>3. 権限一覧 *</x:v>
-      </x:c>
-      <x:c r="N13" s="168" t="str">
-        <x:v>3. 権限一覧 *</x:v>
-      </x:c>
-      <x:c r="O13" s="168" t="str">
-        <x:v>3. 権限一覧 *</x:v>
-      </x:c>
-      <x:c r="P13" s="169" t="str">
-        <x:v>3. 権限一覧 *</x:v>
-      </x:c>
+      <x:c r="E13" s="168" t="str"/>
+      <x:c r="F13" s="168" t="str"/>
+      <x:c r="G13" s="168" t="str"/>
+      <x:c r="H13" s="168" t="str"/>
+      <x:c r="I13" s="168" t="str"/>
+      <x:c r="J13" s="168" t="str"/>
+      <x:c r="K13" s="168" t="str"/>
+      <x:c r="L13" s="168" t="str"/>
+      <x:c r="M13" s="168" t="str"/>
+      <x:c r="N13" s="168" t="str"/>
+      <x:c r="O13" s="168" t="str"/>
+      <x:c r="P13" s="169" t="str"/>
     </x:row>
     <x:row r="14" ht="21" customHeight="1">
-      <x:c r="A14" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B14" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C14" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A14" s="110" t="str"/>
+      <x:c r="B14" s="111" t="str"/>
+      <x:c r="C14" s="112" t="str"/>
       <x:c r="D14" s="174" t="str">
         <x:v>☑ employee:read</x:v>
       </x:c>
-      <x:c r="E14" s="174" t="str">
-        <x:v>☑ employee:read</x:v>
-      </x:c>
-      <x:c r="F14" s="174" t="str">
-        <x:v>☑ employee:read</x:v>
-      </x:c>
-      <x:c r="G14" s="174" t="str">
-        <x:v>☑ employee:read</x:v>
-      </x:c>
-      <x:c r="H14" s="174" t="str">
-        <x:v>☑ employee:read</x:v>
-      </x:c>
-      <x:c r="I14" s="174" t="str">
-        <x:v>☑ employee:read</x:v>
-      </x:c>
+      <x:c r="E14" s="174" t="str"/>
+      <x:c r="F14" s="174" t="str"/>
+      <x:c r="G14" s="174" t="str"/>
+      <x:c r="H14" s="174" t="str"/>
+      <x:c r="I14" s="174" t="str"/>
       <x:c r="J14" s="174" t="str">
         <x:v>☑ employee:write</x:v>
       </x:c>
-      <x:c r="K14" s="174" t="str">
-        <x:v>☑ employee:write</x:v>
-      </x:c>
-      <x:c r="L14" s="174" t="str">
-        <x:v>☑ employee:write</x:v>
-      </x:c>
-      <x:c r="M14" s="174" t="str">
-        <x:v>☑ employee:write</x:v>
-      </x:c>
-      <x:c r="N14" s="174" t="str">
-        <x:v>☑ employee:write</x:v>
-      </x:c>
-      <x:c r="O14" s="174" t="str">
-        <x:v>☑ employee:write</x:v>
-      </x:c>
+      <x:c r="K14" s="174" t="str"/>
+      <x:c r="L14" s="174" t="str"/>
+      <x:c r="M14" s="174" t="str"/>
+      <x:c r="N14" s="174" t="str"/>
+      <x:c r="O14" s="174" t="str"/>
       <x:c r="P14" s="48"/>
     </x:row>
     <x:row r="15" ht="21" customHeight="1">
-      <x:c r="A15" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B15" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C15" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A15" s="110" t="str"/>
+      <x:c r="B15" s="111" t="str"/>
+      <x:c r="C15" s="112" t="str"/>
       <x:c r="D15" s="48"/>
       <x:c r="E15" s="48"/>
       <x:c r="F15" s="48"/>
@@ -7916,99 +5962,31 @@
       <x:c r="P15" s="48"/>
     </x:row>
     <x:row r="16" ht="21" customHeight="1">
-      <x:c r="A16" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B16" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C16" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A16" s="110" t="str"/>
+      <x:c r="B16" s="111" t="str"/>
+      <x:c r="C16" s="112" t="str"/>
       <x:c r="D16" s="174" t="str">
         <x:v>☑ project:read</x:v>
       </x:c>
-      <x:c r="E16" s="174" t="str">
-        <x:v>☑ project:read</x:v>
-      </x:c>
-      <x:c r="F16" s="174" t="str">
-        <x:v>☑ project:read</x:v>
-      </x:c>
-      <x:c r="G16" s="174" t="str">
-        <x:v>☑ project:read</x:v>
-      </x:c>
-      <x:c r="H16" s="174" t="str">
-        <x:v>☑ project:read</x:v>
-      </x:c>
-      <x:c r="I16" s="174" t="str">
-        <x:v>☑ project:read</x:v>
-      </x:c>
+      <x:c r="E16" s="174" t="str"/>
+      <x:c r="F16" s="174" t="str"/>
+      <x:c r="G16" s="174" t="str"/>
+      <x:c r="H16" s="174" t="str"/>
+      <x:c r="I16" s="174" t="str"/>
       <x:c r="J16" s="174" t="str">
         <x:v>☑ project:write</x:v>
       </x:c>
-      <x:c r="K16" s="174" t="str">
-        <x:v>☑ project:write</x:v>
-      </x:c>
-      <x:c r="L16" s="174" t="str">
-        <x:v>☑ project:write</x:v>
-      </x:c>
-      <x:c r="M16" s="174" t="str">
-        <x:v>☑ project:write</x:v>
-      </x:c>
-      <x:c r="N16" s="174" t="str">
-        <x:v>☑ project:write</x:v>
-      </x:c>
-      <x:c r="O16" s="174" t="str">
-        <x:v>☑ project:write</x:v>
-      </x:c>
+      <x:c r="K16" s="174" t="str"/>
+      <x:c r="L16" s="174" t="str"/>
+      <x:c r="M16" s="174" t="str"/>
+      <x:c r="N16" s="174" t="str"/>
+      <x:c r="O16" s="174" t="str"/>
       <x:c r="P16" s="48"/>
     </x:row>
     <x:row r="17" ht="21" customHeight="1">
-      <x:c r="A17" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B17" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C17" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A17" s="110" t="str"/>
+      <x:c r="B17" s="111" t="str"/>
+      <x:c r="C17" s="112" t="str"/>
       <x:c r="D17" s="48"/>
       <x:c r="E17" s="48"/>
       <x:c r="F17" s="48"/>
@@ -8024,99 +6002,31 @@
       <x:c r="P17" s="48"/>
     </x:row>
     <x:row r="18" ht="21" customHeight="1">
-      <x:c r="A18" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B18" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C18" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A18" s="110" t="str"/>
+      <x:c r="B18" s="111" t="str"/>
+      <x:c r="C18" s="112" t="str"/>
       <x:c r="D18" s="174" t="str">
         <x:v>☑ task:read</x:v>
       </x:c>
-      <x:c r="E18" s="174" t="str">
-        <x:v>☑ task:read</x:v>
-      </x:c>
-      <x:c r="F18" s="174" t="str">
-        <x:v>☑ task:read</x:v>
-      </x:c>
-      <x:c r="G18" s="174" t="str">
-        <x:v>☑ task:read</x:v>
-      </x:c>
-      <x:c r="H18" s="174" t="str">
-        <x:v>☑ task:read</x:v>
-      </x:c>
-      <x:c r="I18" s="174" t="str">
-        <x:v>☑ task:read</x:v>
-      </x:c>
+      <x:c r="E18" s="174" t="str"/>
+      <x:c r="F18" s="174" t="str"/>
+      <x:c r="G18" s="174" t="str"/>
+      <x:c r="H18" s="174" t="str"/>
+      <x:c r="I18" s="174" t="str"/>
       <x:c r="J18" s="174" t="str">
         <x:v>☑ task:write</x:v>
       </x:c>
-      <x:c r="K18" s="174" t="str">
-        <x:v>☑ task:write</x:v>
-      </x:c>
-      <x:c r="L18" s="174" t="str">
-        <x:v>☑ task:write</x:v>
-      </x:c>
-      <x:c r="M18" s="174" t="str">
-        <x:v>☑ task:write</x:v>
-      </x:c>
-      <x:c r="N18" s="174" t="str">
-        <x:v>☑ task:write</x:v>
-      </x:c>
-      <x:c r="O18" s="174" t="str">
-        <x:v>☑ task:write</x:v>
-      </x:c>
+      <x:c r="K18" s="174" t="str"/>
+      <x:c r="L18" s="174" t="str"/>
+      <x:c r="M18" s="174" t="str"/>
+      <x:c r="N18" s="174" t="str"/>
+      <x:c r="O18" s="174" t="str"/>
       <x:c r="P18" s="48"/>
     </x:row>
     <x:row r="19" ht="21" customHeight="1">
-      <x:c r="A19" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B19" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C19" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A19" s="110" t="str"/>
+      <x:c r="B19" s="111" t="str"/>
+      <x:c r="C19" s="112" t="str"/>
       <x:c r="D19" s="48"/>
       <x:c r="E19" s="48"/>
       <x:c r="F19" s="48"/>
@@ -8132,99 +6042,31 @@
       <x:c r="P19" s="48"/>
     </x:row>
     <x:row r="20" ht="21" customHeight="1">
-      <x:c r="A20" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B20" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C20" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A20" s="110" t="str"/>
+      <x:c r="B20" s="111" t="str"/>
+      <x:c r="C20" s="112" t="str"/>
       <x:c r="D20" s="129" t="str">
         <x:v>☑ report:read</x:v>
       </x:c>
-      <x:c r="E20" s="129" t="str">
-        <x:v>☑ report:read</x:v>
-      </x:c>
-      <x:c r="F20" s="129" t="str">
-        <x:v>☑ report:read</x:v>
-      </x:c>
-      <x:c r="G20" s="129" t="str">
-        <x:v>☑ report:read</x:v>
-      </x:c>
-      <x:c r="H20" s="129" t="str">
-        <x:v>☑ report:read</x:v>
-      </x:c>
-      <x:c r="I20" s="129" t="str">
-        <x:v>☑ report:read</x:v>
-      </x:c>
+      <x:c r="E20" s="129" t="str"/>
+      <x:c r="F20" s="129" t="str"/>
+      <x:c r="G20" s="129" t="str"/>
+      <x:c r="H20" s="129" t="str"/>
+      <x:c r="I20" s="129" t="str"/>
       <x:c r="J20" s="129" t="str">
         <x:v>☑ system:admin</x:v>
       </x:c>
-      <x:c r="K20" s="129" t="str">
-        <x:v>☑ system:admin</x:v>
-      </x:c>
-      <x:c r="L20" s="129" t="str">
-        <x:v>☑ system:admin</x:v>
-      </x:c>
-      <x:c r="M20" s="129" t="str">
-        <x:v>☑ system:admin</x:v>
-      </x:c>
-      <x:c r="N20" s="129" t="str">
-        <x:v>☑ system:admin</x:v>
-      </x:c>
-      <x:c r="O20" s="129" t="str">
-        <x:v>☑ system:admin</x:v>
-      </x:c>
+      <x:c r="K20" s="129" t="str"/>
+      <x:c r="L20" s="129" t="str"/>
+      <x:c r="M20" s="129" t="str"/>
+      <x:c r="N20" s="129" t="str"/>
+      <x:c r="O20" s="129" t="str"/>
       <x:c r="P20" s="48"/>
     </x:row>
     <x:row r="21" ht="21" customHeight="1">
-      <x:c r="A21" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B21" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C21" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A21" s="110" t="str"/>
+      <x:c r="B21" s="111" t="str"/>
+      <x:c r="C21" s="112" t="str"/>
       <x:c r="D21" s="48"/>
       <x:c r="E21" s="48"/>
       <x:c r="F21" s="48"/>
@@ -8240,33 +6082,9 @@
       <x:c r="P21" s="48"/>
     </x:row>
     <x:row r="22" ht="21" customHeight="1">
-      <x:c r="A22" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B22" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C22" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A22" s="110" t="str"/>
+      <x:c r="B22" s="111" t="str"/>
+      <x:c r="C22" s="112" t="str"/>
       <x:c r="D22" s="48"/>
       <x:c r="E22" s="48"/>
       <x:c r="F22" s="48"/>
@@ -8282,33 +6100,9 @@
       <x:c r="P22" s="48"/>
     </x:row>
     <x:row r="23" ht="21" customHeight="1">
-      <x:c r="A23" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B23" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C23" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A23" s="110" t="str"/>
+      <x:c r="B23" s="111" t="str"/>
+      <x:c r="C23" s="112" t="str"/>
       <x:c r="D23" s="48"/>
       <x:c r="E23" s="48"/>
       <x:c r="F23" s="48"/>
@@ -8324,33 +6118,9 @@
       <x:c r="P23" s="48"/>
     </x:row>
     <x:row r="24" ht="21" customHeight="1">
-      <x:c r="A24" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B24" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C24" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A24" s="110" t="str"/>
+      <x:c r="B24" s="111" t="str"/>
+      <x:c r="C24" s="112" t="str"/>
       <x:c r="D24" s="48"/>
       <x:c r="E24" s="48"/>
       <x:c r="F24" s="48"/>
@@ -8366,33 +6136,9 @@
       <x:c r="P24" s="48"/>
     </x:row>
     <x:row r="25" ht="21" customHeight="1">
-      <x:c r="A25" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B25" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C25" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A25" s="110" t="str"/>
+      <x:c r="B25" s="111" t="str"/>
+      <x:c r="C25" s="112" t="str"/>
       <x:c r="D25" s="48"/>
       <x:c r="E25" s="48"/>
       <x:c r="F25" s="48"/>
@@ -8404,47 +6150,17 @@
       <x:c r="L25" s="183" t="str">
         <x:v>取消</x:v>
       </x:c>
-      <x:c r="M25" s="184" t="str">
-        <x:v>取消</x:v>
-      </x:c>
+      <x:c r="M25" s="184" t="str"/>
       <x:c r="N25" s="199" t="str">
         <x:v>保存</x:v>
       </x:c>
-      <x:c r="O25" s="200" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="P25" s="201" t="str">
-        <x:v>保存</x:v>
-      </x:c>
+      <x:c r="O25" s="200" t="str"/>
+      <x:c r="P25" s="201" t="str"/>
     </x:row>
     <x:row r="26" ht="21" customHeight="1">
-      <x:c r="A26" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B26" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C26" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A26" s="110" t="str"/>
+      <x:c r="B26" s="111" t="str"/>
+      <x:c r="C26" s="112" t="str"/>
       <x:c r="D26" s="48"/>
       <x:c r="E26" s="48"/>
       <x:c r="F26" s="48"/>
@@ -8453,50 +6169,16 @@
       <x:c r="I26" s="48"/>
       <x:c r="J26" s="48"/>
       <x:c r="K26" s="48"/>
-      <x:c r="L26" s="185" t="str">
-        <x:v>取消</x:v>
-      </x:c>
-      <x:c r="M26" s="186" t="str">
-        <x:v>取消</x:v>
-      </x:c>
-      <x:c r="N26" s="202" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="O26" s="203" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="P26" s="204" t="str">
-        <x:v>保存</x:v>
-      </x:c>
+      <x:c r="L26" s="185" t="str"/>
+      <x:c r="M26" s="186" t="str"/>
+      <x:c r="N26" s="202" t="str"/>
+      <x:c r="O26" s="203" t="str"/>
+      <x:c r="P26" s="204" t="str"/>
     </x:row>
     <x:row r="27" ht="21" customHeight="1">
-      <x:c r="A27" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B27" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C27" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A27" s="110" t="str"/>
+      <x:c r="B27" s="111" t="str"/>
+      <x:c r="C27" s="112" t="str"/>
       <x:c r="D27" s="48"/>
       <x:c r="E27" s="48"/>
       <x:c r="F27" s="48"/>
@@ -8512,33 +6194,9 @@
       <x:c r="P27" s="48"/>
     </x:row>
     <x:row r="28" ht="21" customHeight="1">
-      <x:c r="A28" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B28" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C28" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A28" s="110" t="str"/>
+      <x:c r="B28" s="111" t="str"/>
+      <x:c r="C28" s="112" t="str"/>
       <x:c r="D28" s="48"/>
       <x:c r="E28" s="48"/>
       <x:c r="F28" s="48"/>
@@ -8554,33 +6212,9 @@
       <x:c r="P28" s="48"/>
     </x:row>
     <x:row r="29" ht="21" customHeight="1">
-      <x:c r="A29" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B29" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C29" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A29" s="110" t="str"/>
+      <x:c r="B29" s="111" t="str"/>
+      <x:c r="C29" s="112" t="str"/>
       <x:c r="D29" s="48"/>
       <x:c r="E29" s="48"/>
       <x:c r="F29" s="48"/>
@@ -8596,33 +6230,9 @@
       <x:c r="P29" s="48"/>
     </x:row>
     <x:row r="30" ht="21" customHeight="1">
-      <x:c r="A30" s="113" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B30" s="114" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C30" s="115" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A30" s="113" t="str"/>
+      <x:c r="B30" s="114" t="str"/>
+      <x:c r="C30" s="115" t="str"/>
       <x:c r="D30" s="48"/>
       <x:c r="E30" s="48"/>
       <x:c r="F30" s="48"/>
@@ -8704,7 +6314,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -8730,101 +6340,43 @@
       <x:c r="A1" s="52" t="str">
         <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
       </x:c>
-      <x:c r="B1" s="52" t="str">
-        <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="C1" s="52" t="str">
-        <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="D1" s="52" t="str">
-        <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="E1" s="52" t="str">
-        <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="F1" s="52" t="str">
-        <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="G1" s="52" t="str">
-        <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="H1" s="52" t="str">
-        <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="I1" s="52" t="str">
-        <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="J1" s="52" t="str">
-        <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="K1" s="52" t="str">
-        <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="L1" s="52" t="str">
-        <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="M1" s="52" t="str">
-        <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="N1" s="52" t="str">
-        <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="O1" s="52" t="str">
-        <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="P1" s="52" t="str">
-        <x:v>SCR-025  操作ログ  画面レイアウト</x:v>
-      </x:c>
+      <x:c r="B1" s="52" t="str"/>
+      <x:c r="C1" s="52" t="str"/>
+      <x:c r="D1" s="52" t="str"/>
+      <x:c r="E1" s="52" t="str"/>
+      <x:c r="F1" s="52" t="str"/>
+      <x:c r="G1" s="52" t="str"/>
+      <x:c r="H1" s="52" t="str"/>
+      <x:c r="I1" s="52" t="str"/>
+      <x:c r="J1" s="52" t="str"/>
+      <x:c r="K1" s="52" t="str"/>
+      <x:c r="L1" s="52" t="str"/>
+      <x:c r="M1" s="52" t="str"/>
+      <x:c r="N1" s="52" t="str"/>
+      <x:c r="O1" s="52" t="str"/>
+      <x:c r="P1" s="52" t="str"/>
     </x:row>
     <x:row r="2" ht="21" customHeight="1">
       <x:c r="A2" s="54" t="str">
         <x:v>画面ID: SCR-025    画面名: 操作ログ</x:v>
       </x:c>
-      <x:c r="B2" s="54" t="str">
-        <x:v>画面ID: SCR-025    画面名: 操作ログ</x:v>
-      </x:c>
-      <x:c r="C2" s="54" t="str">
-        <x:v>画面ID: SCR-025    画面名: 操作ログ</x:v>
-      </x:c>
-      <x:c r="D2" s="54" t="str">
-        <x:v>画面ID: SCR-025    画面名: 操作ログ</x:v>
-      </x:c>
-      <x:c r="E2" s="54" t="str">
-        <x:v>画面ID: SCR-025    画面名: 操作ログ</x:v>
-      </x:c>
-      <x:c r="F2" s="54" t="str">
-        <x:v>画面ID: SCR-025    画面名: 操作ログ</x:v>
-      </x:c>
-      <x:c r="G2" s="54" t="str">
-        <x:v>画面ID: SCR-025    画面名: 操作ログ</x:v>
-      </x:c>
-      <x:c r="H2" s="54" t="str">
-        <x:v>画面ID: SCR-025    画面名: 操作ログ</x:v>
-      </x:c>
-      <x:c r="I2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="J2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="K2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="L2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="M2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="N2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="O2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="P2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
+      <x:c r="B2" s="54" t="str"/>
+      <x:c r="C2" s="54" t="str"/>
+      <x:c r="D2" s="54" t="str"/>
+      <x:c r="E2" s="54" t="str"/>
+      <x:c r="F2" s="54" t="str"/>
+      <x:c r="G2" s="54" t="str"/>
+      <x:c r="H2" s="54" t="str"/>
+      <x:c r="I2" s="370" t="str">
+        <x:v>Ver.2.5    2026-09-24</x:v>
+      </x:c>
+      <x:c r="J2" s="55" t="str"/>
+      <x:c r="K2" s="55" t="str"/>
+      <x:c r="L2" s="55" t="str"/>
+      <x:c r="M2" s="55" t="str"/>
+      <x:c r="N2" s="55" t="str"/>
+      <x:c r="O2" s="55" t="str"/>
+      <x:c r="P2" s="55" t="str"/>
     </x:row>
     <x:row r="3" ht="21" customHeight="1">
       <x:c r="A3" s="48"/>
@@ -8848,101 +6400,39 @@
       <x:c r="A4" s="72" t="str">
         <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
       </x:c>
-      <x:c r="B4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="C4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="D4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="E4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="F4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="G4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="H4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="I4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="J4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="K4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="L4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="M4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="N4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="O4" s="73" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="P4" s="74" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
+      <x:c r="B4" s="73" t="str"/>
+      <x:c r="C4" s="73" t="str"/>
+      <x:c r="D4" s="73" t="str"/>
+      <x:c r="E4" s="73" t="str"/>
+      <x:c r="F4" s="73" t="str"/>
+      <x:c r="G4" s="73" t="str"/>
+      <x:c r="H4" s="73" t="str"/>
+      <x:c r="I4" s="73" t="str"/>
+      <x:c r="J4" s="73" t="str"/>
+      <x:c r="K4" s="73" t="str"/>
+      <x:c r="L4" s="73" t="str"/>
+      <x:c r="M4" s="73" t="str"/>
+      <x:c r="N4" s="73" t="str"/>
+      <x:c r="O4" s="73" t="str"/>
+      <x:c r="P4" s="74" t="str"/>
     </x:row>
     <x:row r="5" ht="21" customHeight="1">
-      <x:c r="A5" s="75" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="B5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="C5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="D5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="E5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="F5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="G5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="H5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="I5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="J5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="K5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="L5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="M5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="N5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="O5" s="76" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="P5" s="77" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
+      <x:c r="A5" s="75" t="str"/>
+      <x:c r="B5" s="76" t="str"/>
+      <x:c r="C5" s="76" t="str"/>
+      <x:c r="D5" s="76" t="str"/>
+      <x:c r="E5" s="76" t="str"/>
+      <x:c r="F5" s="76" t="str"/>
+      <x:c r="G5" s="76" t="str"/>
+      <x:c r="H5" s="76" t="str"/>
+      <x:c r="I5" s="76" t="str"/>
+      <x:c r="J5" s="76" t="str"/>
+      <x:c r="K5" s="76" t="str"/>
+      <x:c r="L5" s="76" t="str"/>
+      <x:c r="M5" s="76" t="str"/>
+      <x:c r="N5" s="76" t="str"/>
+      <x:c r="O5" s="76" t="str"/>
+      <x:c r="P5" s="77" t="str"/>
     </x:row>
     <x:row r="6" ht="21" customHeight="1">
       <x:c r="A6" s="107" t="str">
@@ -8954,212 +6444,66 @@
 通知
 System</x:v>
       </x:c>
-      <x:c r="B6" s="108" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C6" s="109" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="B6" s="108" t="str"/>
+      <x:c r="C6" s="109" t="str"/>
       <x:c r="D6" s="118" t="str">
         <x:v>Home  &gt;  操作ログ</x:v>
       </x:c>
-      <x:c r="E6" s="118" t="str">
-        <x:v>Home  &gt;  操作ログ</x:v>
-      </x:c>
-      <x:c r="F6" s="118" t="str">
-        <x:v>Home  &gt;  操作ログ</x:v>
-      </x:c>
-      <x:c r="G6" s="118" t="str">
-        <x:v>Home  &gt;  操作ログ</x:v>
-      </x:c>
-      <x:c r="H6" s="118" t="str">
-        <x:v>Home  &gt;  操作ログ</x:v>
-      </x:c>
-      <x:c r="I6" s="118" t="str">
-        <x:v>Home  &gt;  操作ログ</x:v>
-      </x:c>
-      <x:c r="J6" s="118" t="str">
-        <x:v>Home  &gt;  操作ログ</x:v>
-      </x:c>
-      <x:c r="K6" s="118" t="str">
-        <x:v>Home  &gt;  操作ログ</x:v>
-      </x:c>
-      <x:c r="L6" s="118" t="str">
-        <x:v>Home  &gt;  操作ログ</x:v>
-      </x:c>
-      <x:c r="M6" s="118" t="str">
-        <x:v>Home  &gt;  操作ログ</x:v>
-      </x:c>
-      <x:c r="N6" s="118" t="str">
-        <x:v>Home  &gt;  操作ログ</x:v>
-      </x:c>
-      <x:c r="O6" s="118" t="str">
-        <x:v>Home  &gt;  操作ログ</x:v>
-      </x:c>
-      <x:c r="P6" s="118" t="str">
-        <x:v>Home  &gt;  操作ログ</x:v>
-      </x:c>
+      <x:c r="E6" s="118" t="str"/>
+      <x:c r="F6" s="118" t="str"/>
+      <x:c r="G6" s="118" t="str"/>
+      <x:c r="H6" s="118" t="str"/>
+      <x:c r="I6" s="118" t="str"/>
+      <x:c r="J6" s="118" t="str"/>
+      <x:c r="K6" s="118" t="str"/>
+      <x:c r="L6" s="118" t="str"/>
+      <x:c r="M6" s="118" t="str"/>
+      <x:c r="N6" s="118" t="str"/>
+      <x:c r="O6" s="118" t="str"/>
+      <x:c r="P6" s="118" t="str"/>
     </x:row>
     <x:row r="7" ht="21" customHeight="1">
-      <x:c r="A7" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B7" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C7" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A7" s="110" t="str"/>
+      <x:c r="B7" s="111" t="str"/>
+      <x:c r="C7" s="112" t="str"/>
       <x:c r="D7" s="120" t="str">
         <x:v>操作ログ</x:v>
       </x:c>
-      <x:c r="E7" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="F7" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="G7" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="H7" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="I7" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="J7" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="K7" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="L7" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
+      <x:c r="E7" s="120" t="str"/>
+      <x:c r="F7" s="120" t="str"/>
+      <x:c r="G7" s="120" t="str"/>
+      <x:c r="H7" s="120" t="str"/>
+      <x:c r="I7" s="120" t="str"/>
+      <x:c r="J7" s="120" t="str"/>
+      <x:c r="K7" s="120" t="str"/>
+      <x:c r="L7" s="120" t="str"/>
       <x:c r="M7" s="48"/>
       <x:c r="N7" s="48"/>
       <x:c r="O7" s="48"/>
       <x:c r="P7" s="48"/>
     </x:row>
     <x:row r="8" ht="21" customHeight="1">
-      <x:c r="A8" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B8" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C8" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D8" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="E8" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="F8" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="G8" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="H8" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="I8" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="J8" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="K8" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
-      <x:c r="L8" s="120" t="str">
-        <x:v>操作ログ</x:v>
-      </x:c>
+      <x:c r="A8" s="110" t="str"/>
+      <x:c r="B8" s="111" t="str"/>
+      <x:c r="C8" s="112" t="str"/>
+      <x:c r="D8" s="120" t="str"/>
+      <x:c r="E8" s="120" t="str"/>
+      <x:c r="F8" s="120" t="str"/>
+      <x:c r="G8" s="120" t="str"/>
+      <x:c r="H8" s="120" t="str"/>
+      <x:c r="I8" s="120" t="str"/>
+      <x:c r="J8" s="120" t="str"/>
+      <x:c r="K8" s="120" t="str"/>
+      <x:c r="L8" s="120" t="str"/>
       <x:c r="M8" s="48"/>
       <x:c r="N8" s="48"/>
       <x:c r="O8" s="48"/>
       <x:c r="P8" s="48"/>
     </x:row>
     <x:row r="9" ht="21" customHeight="1">
-      <x:c r="A9" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B9" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C9" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A9" s="110" t="str"/>
+      <x:c r="B9" s="111" t="str"/>
+      <x:c r="C9" s="112" t="str"/>
       <x:c r="D9" s="48"/>
       <x:c r="E9" s="48"/>
       <x:c r="F9" s="48"/>
@@ -9175,159 +6519,55 @@
       <x:c r="P9" s="48"/>
     </x:row>
     <x:row r="10" ht="21" customHeight="1">
-      <x:c r="A10" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B10" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C10" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A10" s="110" t="str"/>
+      <x:c r="B10" s="111" t="str"/>
+      <x:c r="C10" s="112" t="str"/>
       <x:c r="D10" s="122" t="str">
         <x:v>検索条件</x:v>
       </x:c>
-      <x:c r="E10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="F10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="G10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="H10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="I10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="J10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="K10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="L10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="M10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="N10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="O10" s="123" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
-      <x:c r="P10" s="124" t="str">
-        <x:v>検索条件</x:v>
-      </x:c>
+      <x:c r="E10" s="123" t="str"/>
+      <x:c r="F10" s="123" t="str"/>
+      <x:c r="G10" s="123" t="str"/>
+      <x:c r="H10" s="123" t="str"/>
+      <x:c r="I10" s="123" t="str"/>
+      <x:c r="J10" s="123" t="str"/>
+      <x:c r="K10" s="123" t="str"/>
+      <x:c r="L10" s="123" t="str"/>
+      <x:c r="M10" s="123" t="str"/>
+      <x:c r="N10" s="123" t="str"/>
+      <x:c r="O10" s="123" t="str"/>
+      <x:c r="P10" s="124" t="str"/>
     </x:row>
     <x:row r="11" ht="21" customHeight="1">
-      <x:c r="A11" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B11" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C11" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A11" s="110" t="str"/>
+      <x:c r="B11" s="111" t="str"/>
+      <x:c r="C11" s="112" t="str"/>
       <x:c r="D11" s="126" t="str">
         <x:v>日時</x:v>
       </x:c>
-      <x:c r="E11" s="126" t="str">
-        <x:v>日時</x:v>
-      </x:c>
+      <x:c r="E11" s="126" t="str"/>
       <x:c r="F11" s="129" t="str"/>
       <x:c r="G11" s="129" t="str"/>
       <x:c r="H11" s="126" t="str">
         <x:v>ユーザー</x:v>
       </x:c>
-      <x:c r="I11" s="126" t="str">
-        <x:v>ユーザー</x:v>
-      </x:c>
+      <x:c r="I11" s="126" t="str"/>
       <x:c r="J11" s="129" t="str"/>
       <x:c r="K11" s="129" t="str"/>
       <x:c r="L11" s="126" t="str">
         <x:v>Module</x:v>
       </x:c>
-      <x:c r="M11" s="126" t="str">
-        <x:v>Module</x:v>
-      </x:c>
+      <x:c r="M11" s="126" t="str"/>
       <x:c r="N11" s="129" t="str">
         <x:v>すべて  ▼</x:v>
       </x:c>
-      <x:c r="O11" s="129" t="str">
-        <x:v>すべて  ▼</x:v>
-      </x:c>
+      <x:c r="O11" s="129" t="str"/>
       <x:c r="P11" s="48"/>
     </x:row>
     <x:row r="12" ht="21" customHeight="1">
-      <x:c r="A12" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B12" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C12" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A12" s="110" t="str"/>
+      <x:c r="B12" s="111" t="str"/>
+      <x:c r="C12" s="112" t="str"/>
       <x:c r="D12" s="48"/>
       <x:c r="E12" s="48"/>
       <x:c r="F12" s="48"/>
@@ -9343,91 +6583,35 @@
       <x:c r="P12" s="48"/>
     </x:row>
     <x:row r="13" ht="21" customHeight="1">
-      <x:c r="A13" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B13" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C13" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A13" s="110" t="str"/>
+      <x:c r="B13" s="111" t="str"/>
+      <x:c r="C13" s="112" t="str"/>
       <x:c r="D13" s="126" t="str">
         <x:v>Action</x:v>
       </x:c>
-      <x:c r="E13" s="126" t="str">
-        <x:v>Action</x:v>
-      </x:c>
+      <x:c r="E13" s="126" t="str"/>
       <x:c r="F13" s="129" t="str"/>
       <x:c r="G13" s="129" t="str"/>
       <x:c r="H13" s="126" t="str">
         <x:v>結果</x:v>
       </x:c>
-      <x:c r="I13" s="126" t="str">
-        <x:v>結果</x:v>
-      </x:c>
+      <x:c r="I13" s="126" t="str"/>
       <x:c r="J13" s="129" t="str"/>
       <x:c r="K13" s="129" t="str"/>
       <x:c r="L13" s="126" t="str">
         <x:v>Trace ID</x:v>
       </x:c>
-      <x:c r="M13" s="126" t="str">
-        <x:v>Trace ID</x:v>
-      </x:c>
+      <x:c r="M13" s="126" t="str"/>
       <x:c r="N13" s="129" t="str">
         <x:v>すべて  ▼</x:v>
       </x:c>
-      <x:c r="O13" s="129" t="str">
-        <x:v>すべて  ▼</x:v>
-      </x:c>
+      <x:c r="O13" s="129" t="str"/>
       <x:c r="P13" s="48"/>
     </x:row>
     <x:row r="14" ht="21" customHeight="1">
-      <x:c r="A14" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B14" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C14" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A14" s="110" t="str"/>
+      <x:c r="B14" s="111" t="str"/>
+      <x:c r="C14" s="112" t="str"/>
       <x:c r="D14" s="48"/>
       <x:c r="E14" s="48"/>
       <x:c r="F14" s="48"/>
@@ -9443,33 +6627,9 @@
       <x:c r="P14" s="48"/>
     </x:row>
     <x:row r="15" ht="21" customHeight="1">
-      <x:c r="A15" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B15" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C15" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A15" s="110" t="str"/>
+      <x:c r="B15" s="111" t="str"/>
+      <x:c r="C15" s="112" t="str"/>
       <x:c r="D15" s="48"/>
       <x:c r="E15" s="48"/>
       <x:c r="F15" s="48"/>
@@ -9481,47 +6641,17 @@
       <x:c r="L15" s="135" t="str">
         <x:v>クリア</x:v>
       </x:c>
-      <x:c r="M15" s="136" t="str">
-        <x:v>クリア</x:v>
-      </x:c>
+      <x:c r="M15" s="136" t="str"/>
       <x:c r="N15" s="143" t="str">
         <x:v>検索</x:v>
       </x:c>
-      <x:c r="O15" s="144" t="str">
-        <x:v>検索</x:v>
-      </x:c>
-      <x:c r="P15" s="145" t="str">
-        <x:v>検索</x:v>
-      </x:c>
+      <x:c r="O15" s="144" t="str"/>
+      <x:c r="P15" s="145" t="str"/>
     </x:row>
     <x:row r="16" ht="21" customHeight="1">
-      <x:c r="A16" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B16" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C16" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A16" s="110" t="str"/>
+      <x:c r="B16" s="111" t="str"/>
+      <x:c r="C16" s="112" t="str"/>
       <x:c r="D16" s="48"/>
       <x:c r="E16" s="48"/>
       <x:c r="F16" s="48"/>
@@ -9537,305 +6667,137 @@
       <x:c r="P16" s="48"/>
     </x:row>
     <x:row r="17" ht="21" customHeight="1">
-      <x:c r="A17" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B17" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C17" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A17" s="110" t="str"/>
+      <x:c r="B17" s="111" t="str"/>
+      <x:c r="C17" s="112" t="str"/>
       <x:c r="D17" s="150" t="str">
         <x:v>日時</x:v>
       </x:c>
-      <x:c r="E17" s="150" t="str">
-        <x:v>日時</x:v>
-      </x:c>
+      <x:c r="E17" s="150" t="str"/>
       <x:c r="F17" s="150" t="str">
         <x:v>ユーザー</x:v>
       </x:c>
-      <x:c r="G17" s="150" t="str">
-        <x:v>ユーザー</x:v>
-      </x:c>
+      <x:c r="G17" s="150" t="str"/>
       <x:c r="H17" s="150" t="str">
         <x:v>Module</x:v>
       </x:c>
-      <x:c r="I17" s="150" t="str">
-        <x:v>Module</x:v>
-      </x:c>
+      <x:c r="I17" s="150" t="str"/>
       <x:c r="J17" s="150" t="str">
         <x:v>Action</x:v>
       </x:c>
-      <x:c r="K17" s="150" t="str">
-        <x:v>Action</x:v>
-      </x:c>
+      <x:c r="K17" s="150" t="str"/>
       <x:c r="L17" s="150" t="str">
         <x:v>結果</x:v>
       </x:c>
-      <x:c r="M17" s="150" t="str">
-        <x:v>結果</x:v>
-      </x:c>
+      <x:c r="M17" s="150" t="str"/>
       <x:c r="N17" s="150" t="str">
         <x:v>IP</x:v>
       </x:c>
-      <x:c r="O17" s="150" t="str">
-        <x:v>IP</x:v>
-      </x:c>
+      <x:c r="O17" s="150" t="str"/>
       <x:c r="P17" s="150" t="str">
         <x:v>Trace ID</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="21" customHeight="1">
-      <x:c r="A18" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B18" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C18" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A18" s="110" t="str"/>
+      <x:c r="B18" s="111" t="str"/>
+      <x:c r="C18" s="112" t="str"/>
       <x:c r="D18" s="154" t="str">
         <x:v>2026-08-01</x:v>
       </x:c>
-      <x:c r="E18" s="154" t="str">
-        <x:v>2026-08-01</x:v>
-      </x:c>
+      <x:c r="E18" s="154" t="str"/>
       <x:c r="F18" s="154" t="str">
         <x:v>サンプル1</x:v>
       </x:c>
-      <x:c r="G18" s="154" t="str">
-        <x:v>サンプル1</x:v>
-      </x:c>
+      <x:c r="G18" s="154" t="str"/>
       <x:c r="H18" s="154" t="str">
         <x:v>サンプル1</x:v>
       </x:c>
-      <x:c r="I18" s="154" t="str">
-        <x:v>サンプル1</x:v>
-      </x:c>
+      <x:c r="I18" s="154" t="str"/>
       <x:c r="J18" s="154" t="str">
         <x:v>サンプル1</x:v>
       </x:c>
-      <x:c r="K18" s="154" t="str">
-        <x:v>サンプル1</x:v>
-      </x:c>
+      <x:c r="K18" s="154" t="str"/>
       <x:c r="L18" s="154" t="str">
         <x:v>ACTIVE</x:v>
       </x:c>
-      <x:c r="M18" s="154" t="str">
-        <x:v>ACTIVE</x:v>
-      </x:c>
+      <x:c r="M18" s="154" t="str"/>
       <x:c r="N18" s="154" t="str">
         <x:v>サンプル1</x:v>
       </x:c>
-      <x:c r="O18" s="154" t="str">
-        <x:v>サンプル1</x:v>
-      </x:c>
+      <x:c r="O18" s="154" t="str"/>
       <x:c r="P18" s="160" t="str">
         <x:v>0001</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="21" customHeight="1">
-      <x:c r="A19" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B19" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C19" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A19" s="110" t="str"/>
+      <x:c r="B19" s="111" t="str"/>
+      <x:c r="C19" s="112" t="str"/>
       <x:c r="D19" s="158" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
-      <x:c r="E19" s="158" t="str">
-        <x:v>2026-08-02</x:v>
-      </x:c>
+      <x:c r="E19" s="158" t="str"/>
       <x:c r="F19" s="158" t="str">
         <x:v>サンプル2</x:v>
       </x:c>
-      <x:c r="G19" s="158" t="str">
-        <x:v>サンプル2</x:v>
-      </x:c>
+      <x:c r="G19" s="158" t="str"/>
       <x:c r="H19" s="158" t="str">
         <x:v>サンプル2</x:v>
       </x:c>
-      <x:c r="I19" s="158" t="str">
-        <x:v>サンプル2</x:v>
-      </x:c>
+      <x:c r="I19" s="158" t="str"/>
       <x:c r="J19" s="158" t="str">
         <x:v>サンプル2</x:v>
       </x:c>
-      <x:c r="K19" s="158" t="str">
-        <x:v>サンプル2</x:v>
-      </x:c>
+      <x:c r="K19" s="158" t="str"/>
       <x:c r="L19" s="158" t="str">
         <x:v>IN_PROGRESS</x:v>
       </x:c>
-      <x:c r="M19" s="158" t="str">
-        <x:v>IN_PROGRESS</x:v>
-      </x:c>
+      <x:c r="M19" s="158" t="str"/>
       <x:c r="N19" s="158" t="str">
         <x:v>サンプル2</x:v>
       </x:c>
-      <x:c r="O19" s="158" t="str">
-        <x:v>サンプル2</x:v>
-      </x:c>
+      <x:c r="O19" s="158" t="str"/>
       <x:c r="P19" s="162" t="str">
         <x:v>0002</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="21" customHeight="1">
-      <x:c r="A20" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B20" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C20" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A20" s="110" t="str"/>
+      <x:c r="B20" s="111" t="str"/>
+      <x:c r="C20" s="112" t="str"/>
       <x:c r="D20" s="154" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
-      <x:c r="E20" s="154" t="str">
-        <x:v>2026-08-03</x:v>
-      </x:c>
+      <x:c r="E20" s="154" t="str"/>
       <x:c r="F20" s="154" t="str">
         <x:v>サンプル3</x:v>
       </x:c>
-      <x:c r="G20" s="154" t="str">
-        <x:v>サンプル3</x:v>
-      </x:c>
+      <x:c r="G20" s="154" t="str"/>
       <x:c r="H20" s="154" t="str">
         <x:v>サンプル3</x:v>
       </x:c>
-      <x:c r="I20" s="154" t="str">
-        <x:v>サンプル3</x:v>
-      </x:c>
+      <x:c r="I20" s="154" t="str"/>
       <x:c r="J20" s="154" t="str">
         <x:v>サンプル3</x:v>
       </x:c>
-      <x:c r="K20" s="154" t="str">
-        <x:v>サンプル3</x:v>
-      </x:c>
+      <x:c r="K20" s="154" t="str"/>
       <x:c r="L20" s="154" t="str">
         <x:v>IN_PROGRESS</x:v>
       </x:c>
-      <x:c r="M20" s="154" t="str">
-        <x:v>IN_PROGRESS</x:v>
-      </x:c>
+      <x:c r="M20" s="154" t="str"/>
       <x:c r="N20" s="154" t="str">
         <x:v>サンプル3</x:v>
       </x:c>
-      <x:c r="O20" s="154" t="str">
-        <x:v>サンプル3</x:v>
-      </x:c>
+      <x:c r="O20" s="154" t="str"/>
       <x:c r="P20" s="160" t="str">
         <x:v>0003</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="21" customHeight="1">
-      <x:c r="A21" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B21" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C21" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A21" s="110" t="str"/>
+      <x:c r="B21" s="111" t="str"/>
+      <x:c r="C21" s="112" t="str"/>
       <x:c r="D21" s="158" t="str"/>
       <x:c r="E21" s="158" t="str"/>
       <x:c r="F21" s="158" t="str"/>
@@ -9851,33 +6813,9 @@
       <x:c r="P21" s="162" t="str"/>
     </x:row>
     <x:row r="22" ht="21" customHeight="1">
-      <x:c r="A22" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B22" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C22" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A22" s="110" t="str"/>
+      <x:c r="B22" s="111" t="str"/>
+      <x:c r="C22" s="112" t="str"/>
       <x:c r="D22" s="154" t="str"/>
       <x:c r="E22" s="154" t="str"/>
       <x:c r="F22" s="154" t="str"/>
@@ -9893,33 +6831,9 @@
       <x:c r="P22" s="160" t="str"/>
     </x:row>
     <x:row r="23" ht="21" customHeight="1">
-      <x:c r="A23" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B23" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C23" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A23" s="110" t="str"/>
+      <x:c r="B23" s="111" t="str"/>
+      <x:c r="C23" s="112" t="str"/>
       <x:c r="D23" s="158" t="str"/>
       <x:c r="E23" s="158" t="str"/>
       <x:c r="F23" s="158" t="str"/>
@@ -9935,33 +6849,9 @@
       <x:c r="P23" s="162" t="str"/>
     </x:row>
     <x:row r="24" ht="21" customHeight="1">
-      <x:c r="A24" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B24" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C24" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A24" s="110" t="str"/>
+      <x:c r="B24" s="111" t="str"/>
+      <x:c r="C24" s="112" t="str"/>
       <x:c r="D24" s="48"/>
       <x:c r="E24" s="48"/>
       <x:c r="F24" s="48"/>
@@ -9977,95 +6867,33 @@
       <x:c r="P24" s="48"/>
     </x:row>
     <x:row r="25" ht="21" customHeight="1">
-      <x:c r="A25" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B25" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C25" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A25" s="110" t="str"/>
+      <x:c r="B25" s="111" t="str"/>
+      <x:c r="C25" s="112" t="str"/>
       <x:c r="D25" s="163" t="str">
         <x:v>1-20 / 128件</x:v>
       </x:c>
-      <x:c r="E25" s="163" t="str">
-        <x:v>1-20 / 128件</x:v>
-      </x:c>
-      <x:c r="F25" s="163" t="str">
-        <x:v>1-20 / 128件</x:v>
-      </x:c>
-      <x:c r="G25" s="163" t="str">
-        <x:v>1-20 / 128件</x:v>
-      </x:c>
-      <x:c r="H25" s="163" t="str">
-        <x:v>1-20 / 128件</x:v>
-      </x:c>
+      <x:c r="E25" s="163" t="str"/>
+      <x:c r="F25" s="163" t="str"/>
+      <x:c r="G25" s="163" t="str"/>
+      <x:c r="H25" s="163" t="str"/>
       <x:c r="I25" s="48"/>
       <x:c r="J25" s="48"/>
       <x:c r="K25" s="48"/>
       <x:c r="L25" s="135" t="str">
         <x:v>&lt; 前へ</x:v>
       </x:c>
-      <x:c r="M25" s="136" t="str">
-        <x:v>&lt; 前へ</x:v>
-      </x:c>
+      <x:c r="M25" s="136" t="str"/>
       <x:c r="N25" s="135" t="str">
         <x:v>次へ &gt;</x:v>
       </x:c>
-      <x:c r="O25" s="166" t="str">
-        <x:v>次へ &gt;</x:v>
-      </x:c>
-      <x:c r="P25" s="136" t="str">
-        <x:v>次へ &gt;</x:v>
-      </x:c>
+      <x:c r="O25" s="166" t="str"/>
+      <x:c r="P25" s="136" t="str"/>
     </x:row>
     <x:row r="26" ht="21" customHeight="1">
-      <x:c r="A26" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B26" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C26" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A26" s="110" t="str"/>
+      <x:c r="B26" s="111" t="str"/>
+      <x:c r="C26" s="112" t="str"/>
       <x:c r="D26" s="48"/>
       <x:c r="E26" s="48"/>
       <x:c r="F26" s="48"/>
@@ -10081,33 +6909,9 @@
       <x:c r="P26" s="48"/>
     </x:row>
     <x:row r="27" ht="21" customHeight="1">
-      <x:c r="A27" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B27" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C27" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A27" s="110" t="str"/>
+      <x:c r="B27" s="111" t="str"/>
+      <x:c r="C27" s="112" t="str"/>
       <x:c r="D27" s="48"/>
       <x:c r="E27" s="48"/>
       <x:c r="F27" s="48"/>
@@ -10123,33 +6927,9 @@
       <x:c r="P27" s="48"/>
     </x:row>
     <x:row r="28" ht="21" customHeight="1">
-      <x:c r="A28" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B28" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C28" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A28" s="110" t="str"/>
+      <x:c r="B28" s="111" t="str"/>
+      <x:c r="C28" s="112" t="str"/>
       <x:c r="D28" s="48"/>
       <x:c r="E28" s="48"/>
       <x:c r="F28" s="48"/>
@@ -10165,33 +6945,9 @@
       <x:c r="P28" s="48"/>
     </x:row>
     <x:row r="29" ht="21" customHeight="1">
-      <x:c r="A29" s="110" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B29" s="111" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C29" s="112" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A29" s="110" t="str"/>
+      <x:c r="B29" s="111" t="str"/>
+      <x:c r="C29" s="112" t="str"/>
       <x:c r="D29" s="48"/>
       <x:c r="E29" s="48"/>
       <x:c r="F29" s="48"/>
@@ -10207,33 +6963,9 @@
       <x:c r="P29" s="48"/>
     </x:row>
     <x:row r="30" ht="21" customHeight="1">
-      <x:c r="A30" s="113" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B30" s="114" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C30" s="115" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
+      <x:c r="A30" s="113" t="str"/>
+      <x:c r="B30" s="114" t="str"/>
+      <x:c r="C30" s="115" t="str"/>
       <x:c r="D30" s="48"/>
       <x:c r="E30" s="48"/>
       <x:c r="F30" s="48"/>
@@ -10357,4 +7089,122 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="374" t="str">
+        <x:v>12_対象画面INDEX</x:v>
+      </x:c>
+      <x:c r="B1" s="373"/>
+      <x:c r="C1" s="373"/>
+      <x:c r="D1" s="373"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="373"/>
+      <x:c r="B2" s="373"/>
+      <x:c r="C2" s="373"/>
+      <x:c r="D2" s="373"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="373" t="str">
+        <x:v>Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="373"/>
+      <x:c r="C3" s="373"/>
+      <x:c r="D3" s="373"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="373"/>
+      <x:c r="B4" s="373"/>
+      <x:c r="C4" s="373"/>
+      <x:c r="D4" s="373"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="373" t="str">
+        <x:v>BL-2026-09-24 / Review中</x:v>
+      </x:c>
+      <x:c r="B5" s="373"/>
+      <x:c r="C5" s="373"/>
+      <x:c r="D5" s="373"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="373"/>
+      <x:c r="B6" s="373"/>
+      <x:c r="C6" s="373"/>
+      <x:c r="D6" s="373"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="376" t="str">
+        <x:v>画面ID</x:v>
+      </x:c>
+      <x:c r="B7" s="376" t="str">
+        <x:v>画面名</x:v>
+      </x:c>
+      <x:c r="C7" s="376" t="str">
+        <x:v>目的・主要操作</x:v>
+      </x:c>
+      <x:c r="D7" s="376" t="str">
+        <x:v>正本参照</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="378" t="str">
+        <x:v>SCR-023</x:v>
+      </x:c>
+      <x:c r="B8" s="378" t="str">
+        <x:v>ユーザー管理</x:v>
+      </x:c>
+      <x:c r="C8" s="378" t="str">
+        <x:v>検索/詳細遷移</x:v>
+      </x:c>
+      <x:c r="D8" s="378" t="str">
+        <x:v>03／12_画面一覧・20_画面Route定義</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="377" t="str">
+        <x:v>SCR-024</x:v>
+      </x:c>
+      <x:c r="B9" s="377" t="str">
+        <x:v>ロール管理</x:v>
+      </x:c>
+      <x:c r="C9" s="377" t="str">
+        <x:v>検索/詳細遷移</x:v>
+      </x:c>
+      <x:c r="D9" s="377" t="str">
+        <x:v>03／12_画面一覧・20_画面Route定義</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="378" t="str">
+        <x:v>SCR-025</x:v>
+      </x:c>
+      <x:c r="B10" s="378" t="str">
+        <x:v>操作ログ</x:v>
+      </x:c>
+      <x:c r="C10" s="378" t="str">
+        <x:v>検索/詳細遷移</x:v>
+      </x:c>
+      <x:c r="D10" s="378" t="str">
+        <x:v>03／12_画面一覧・20_画面Route定義</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A3:D3"/>
+    <x:mergeCell ref="A5:D5"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>